--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2146,6 +2146,1824 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125598946</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57632</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>769979</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7087051</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125593294</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57632</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mossamyran, Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>769751</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7086871</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125592468</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mossamyran, Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>769672</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7086895</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125592263</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mossamyran, Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>769646</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7086880</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125601124</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mossamyran, Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>769765</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7087093</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125595361</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57632</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Baggöbäcken, Baggöbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>770056</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7086839</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125598057</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57632</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>770047</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7086919</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125598713</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57632</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>770013</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7086998</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125597783</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>770048</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7086917</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125596546</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Baggöbäcken, Baggöbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>770046</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7086894</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125599155</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57632</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>769958</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7087078</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125599815</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sandån, Sandån, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>770018</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7087094</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125595152</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57632</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Baggöbäcken, Baggöbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>770034</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7086842</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -2148,7 +2148,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125598946</v>
+        <v>125595152</v>
       </c>
       <c r="B16" t="n">
         <v>57632</v>
@@ -2189,14 +2189,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
+          <t>Baggöbäcken, Baggöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>769979</v>
+        <v>770034</v>
       </c>
       <c r="R16" t="n">
-        <v>7087051</v>
+        <v>7086842</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125593294</v>
+        <v>125599815</v>
       </c>
       <c r="B17" t="n">
-        <v>57632</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2301,42 +2301,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mossamyran, Mossamyran, Vb</t>
+          <t>Sandån, Sandån, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>769751</v>
+        <v>770018</v>
       </c>
       <c r="R17" t="n">
-        <v>7086871</v>
+        <v>7087094</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2365,7 +2369,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2379,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,10 +2426,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125592468</v>
+        <v>125595361</v>
       </c>
       <c r="B18" t="n">
-        <v>78947</v>
+        <v>57632</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2438,43 +2442,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mossamyran, Mossamyran, Vb</t>
+          <t>Baggöbäcken, Baggöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>769672</v>
+        <v>770056</v>
       </c>
       <c r="R18" t="n">
-        <v>7086895</v>
+        <v>7086839</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2563,10 +2563,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125592263</v>
+        <v>125598946</v>
       </c>
       <c r="B19" t="n">
-        <v>78947</v>
+        <v>57632</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2579,43 +2579,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mossamyran, Mossamyran, Vb</t>
+          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769646</v>
+        <v>769979</v>
       </c>
       <c r="R19" t="n">
-        <v>7086880</v>
+        <v>7087051</v>
       </c>
       <c r="S19" t="n">
         <v>2</v>
@@ -2647,7 +2643,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2657,7 +2653,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2704,7 +2700,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125601124</v>
+        <v>125592468</v>
       </c>
       <c r="B20" t="n">
         <v>78947</v>
@@ -2739,7 +2735,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2753,10 +2749,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769765</v>
+        <v>769672</v>
       </c>
       <c r="R20" t="n">
-        <v>7087093</v>
+        <v>7086895</v>
       </c>
       <c r="S20" t="n">
         <v>2</v>
@@ -2788,7 +2784,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2798,7 +2794,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,10 +2841,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125595361</v>
+        <v>125596546</v>
       </c>
       <c r="B21" t="n">
-        <v>57632</v>
+        <v>78947</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2861,39 +2857,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Baggöbäcken, Baggöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>770056</v>
+        <v>770046</v>
       </c>
       <c r="R21" t="n">
-        <v>7086839</v>
+        <v>7086894</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -2925,7 +2927,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2935,7 +2937,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2944,6 +2946,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2982,7 +2985,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125598057</v>
+        <v>125593294</v>
       </c>
       <c r="B22" t="n">
         <v>57632</v>
@@ -3023,17 +3026,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
+          <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>770047</v>
+        <v>769751</v>
       </c>
       <c r="R22" t="n">
-        <v>7086919</v>
+        <v>7086871</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3062,7 +3065,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3072,7 +3075,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3083,6 +3086,11 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3114,10 +3122,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125598713</v>
+        <v>125592263</v>
       </c>
       <c r="B23" t="n">
-        <v>57632</v>
+        <v>78947</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3130,39 +3138,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
+          <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>770013</v>
+        <v>769646</v>
       </c>
       <c r="R23" t="n">
-        <v>7086998</v>
+        <v>7086880</v>
       </c>
       <c r="S23" t="n">
         <v>2</v>
@@ -3194,7 +3206,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3204,7 +3216,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3251,10 +3263,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125597783</v>
+        <v>125598713</v>
       </c>
       <c r="B24" t="n">
-        <v>57635</v>
+        <v>57632</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3267,16 +3279,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3284,29 +3296,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3315,10 +3308,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>770048</v>
+        <v>770013</v>
       </c>
       <c r="R24" t="n">
-        <v>7086917</v>
+        <v>7086998</v>
       </c>
       <c r="S24" t="n">
         <v>2</v>
@@ -3350,7 +3343,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3360,7 +3353,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3407,10 +3400,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125596546</v>
+        <v>125599155</v>
       </c>
       <c r="B25" t="n">
-        <v>78947</v>
+        <v>57632</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3423,45 +3416,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Baggöbäcken, Baggöbäcken, Vb</t>
+          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>770046</v>
+        <v>769958</v>
       </c>
       <c r="R25" t="n">
-        <v>7086894</v>
+        <v>7087078</v>
       </c>
       <c r="S25" t="n">
         <v>2</v>
@@ -3493,7 +3480,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3503,7 +3490,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3512,7 +3499,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3551,10 +3537,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125599155</v>
+        <v>125601124</v>
       </c>
       <c r="B26" t="n">
-        <v>57632</v>
+        <v>78947</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3567,39 +3553,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
+          <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>769958</v>
+        <v>769765</v>
       </c>
       <c r="R26" t="n">
-        <v>7087078</v>
+        <v>7087093</v>
       </c>
       <c r="S26" t="n">
         <v>2</v>
@@ -3631,7 +3621,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3641,7 +3631,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3688,10 +3678,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125599815</v>
+        <v>125598057</v>
       </c>
       <c r="B27" t="n">
-        <v>78947</v>
+        <v>57632</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3704,46 +3694,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sandån, Sandån, Vb</t>
+          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>770018</v>
+        <v>770047</v>
       </c>
       <c r="R27" t="n">
-        <v>7087094</v>
+        <v>7086919</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3772,7 +3758,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3782,7 +3768,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3793,11 +3779,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -3829,10 +3810,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125595152</v>
+        <v>125597783</v>
       </c>
       <c r="B28" t="n">
-        <v>57632</v>
+        <v>57635</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3845,16 +3826,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3862,22 +3843,41 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Baggöbäcken, Baggöbäcken, Vb</t>
+          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>770034</v>
+        <v>770048</v>
       </c>
       <c r="R28" t="n">
-        <v>7086842</v>
+        <v>7086917</v>
       </c>
       <c r="S28" t="n">
         <v>2</v>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -2285,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125599815</v>
+        <v>125595361</v>
       </c>
       <c r="B17" t="n">
-        <v>78947</v>
+        <v>57632</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2301,46 +2301,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sandån, Sandån, Vb</t>
+          <t>Baggöbäcken, Baggöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>770018</v>
+        <v>770056</v>
       </c>
       <c r="R17" t="n">
-        <v>7087094</v>
+        <v>7086839</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2369,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2379,7 +2375,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2426,10 +2422,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125595361</v>
+        <v>125599815</v>
       </c>
       <c r="B18" t="n">
-        <v>57632</v>
+        <v>78947</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2442,42 +2438,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Baggöbäcken, Baggöbäcken, Vb</t>
+          <t>Sandån, Sandån, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>770056</v>
+        <v>770018</v>
       </c>
       <c r="R18" t="n">
-        <v>7086839</v>
+        <v>7087094</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -2841,10 +2841,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125596546</v>
+        <v>125593294</v>
       </c>
       <c r="B21" t="n">
-        <v>78947</v>
+        <v>57632</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2857,45 +2857,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Baggöbäcken, Baggöbäcken, Vb</t>
+          <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>770046</v>
+        <v>769751</v>
       </c>
       <c r="R21" t="n">
-        <v>7086894</v>
+        <v>7086871</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -2927,7 +2921,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2937,7 +2931,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2946,7 +2940,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2985,10 +2978,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125593294</v>
+        <v>125596546</v>
       </c>
       <c r="B22" t="n">
-        <v>57632</v>
+        <v>78947</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3001,39 +2994,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mossamyran, Mossamyran, Vb</t>
+          <t>Baggöbäcken, Baggöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>769751</v>
+        <v>770046</v>
       </c>
       <c r="R22" t="n">
-        <v>7086871</v>
+        <v>7086894</v>
       </c>
       <c r="S22" t="n">
         <v>2</v>
@@ -3065,7 +3064,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3075,7 +3074,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3084,6 +3083,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2148,15 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125595152</v>
+        <v>125595361</v>
       </c>
       <c r="B16" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2193,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>770034</v>
+        <v>770056</v>
       </c>
       <c r="R16" t="n">
-        <v>7086842</v>
+        <v>7086839</v>
       </c>
       <c r="S16" t="n">
         <v>2</v>
@@ -2228,7 +2223,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2238,7 +2233,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2285,15 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125595361</v>
+        <v>125598713</v>
       </c>
       <c r="B17" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2326,14 +2316,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Baggöbäcken, Baggöbäcken, Vb</t>
+          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>770056</v>
+        <v>770013</v>
       </c>
       <c r="R17" t="n">
-        <v>7086839</v>
+        <v>7086998</v>
       </c>
       <c r="S17" t="n">
         <v>2</v>
@@ -2365,7 +2355,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2365,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2422,15 +2412,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125599815</v>
+        <v>125592468</v>
       </c>
       <c r="B18" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2457,7 +2442,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2467,17 +2452,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sandån, Sandån, Vb</t>
+          <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>770018</v>
+        <v>769672</v>
       </c>
       <c r="R18" t="n">
-        <v>7087094</v>
+        <v>7086895</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2506,7 +2491,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2516,7 +2501,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2563,15 +2548,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125598946</v>
+        <v>125595152</v>
       </c>
       <c r="B19" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2604,14 +2584,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
+          <t>Baggöbäcken, Baggöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>769979</v>
+        <v>770034</v>
       </c>
       <c r="R19" t="n">
-        <v>7087051</v>
+        <v>7086842</v>
       </c>
       <c r="S19" t="n">
         <v>2</v>
@@ -2643,7 +2623,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2653,7 +2633,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,15 +2680,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125592468</v>
+        <v>125601124</v>
       </c>
       <c r="B20" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2735,7 +2710,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2749,10 +2724,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769672</v>
+        <v>769765</v>
       </c>
       <c r="R20" t="n">
-        <v>7086895</v>
+        <v>7087093</v>
       </c>
       <c r="S20" t="n">
         <v>2</v>
@@ -2784,7 +2759,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2794,7 +2769,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2841,15 +2816,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125593294</v>
+        <v>125598946</v>
       </c>
       <c r="B21" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2877,19 +2847,19 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mossamyran, Mossamyran, Vb</t>
+          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769751</v>
+        <v>769979</v>
       </c>
       <c r="R21" t="n">
-        <v>7086871</v>
+        <v>7087051</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -2921,7 +2891,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2931,7 +2901,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2981,12 +2951,7 @@
         <v>125596546</v>
       </c>
       <c r="B22" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3125,12 +3090,7 @@
         <v>125592263</v>
       </c>
       <c r="B23" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3263,15 +3223,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125598713</v>
+        <v>125599815</v>
       </c>
       <c r="B24" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,42 +3234,46 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
+          <t>Sandån, Sandån, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>770013</v>
+        <v>770018</v>
       </c>
       <c r="R24" t="n">
-        <v>7086998</v>
+        <v>7087094</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3343,7 +3302,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3353,7 +3312,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3403,12 +3362,7 @@
         <v>125599155</v>
       </c>
       <c r="B25" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3537,15 +3491,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125601124</v>
+        <v>125598057</v>
       </c>
       <c r="B26" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3553,46 +3502,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mossamyran, Mossamyran, Vb</t>
+          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>769765</v>
+        <v>770047</v>
       </c>
       <c r="R26" t="n">
-        <v>7087093</v>
+        <v>7086919</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3621,7 +3566,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3631,7 +3576,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3642,11 +3587,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3678,15 +3618,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125598057</v>
+        <v>125597783</v>
       </c>
       <c r="B27" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3694,16 +3629,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3711,10 +3646,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3723,13 +3677,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>770047</v>
+        <v>770048</v>
       </c>
       <c r="R27" t="n">
-        <v>7086919</v>
+        <v>7086917</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3758,7 +3712,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3768,7 +3722,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3779,6 +3733,11 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -3807,162 +3766,6 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>125597783</v>
-      </c>
-      <c r="B28" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>770048</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7086917</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Sävar</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Katharina Radloff</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Katharina Radloff</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3767,6 +3767,1081 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125958446</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58019</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mossamyran, Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>769311</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7087040</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125956621</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91223</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mossamyran, Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>769594</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7087023</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125957531</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Mossamyran, Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>769372</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7087093</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125957578</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Mossamyran, Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>769345</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7087087</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125957105</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91192</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mossamyran, Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>769413</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7087074</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125955277</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Mossamyran, Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>769594</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7087023</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125956746</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Mossamyran, Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>769483</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7087082</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125957354</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78967</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Mossamyran, Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>769389</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7087055</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -3772,7 +3772,7 @@
         <v>125958446</v>
       </c>
       <c r="B28" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>125956621</v>
       </c>
       <c r="B29" t="n">
-        <v>91223</v>
+        <v>91224</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4178,57 +4178,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125957578</v>
+        <v>125957105</v>
       </c>
       <c r="B31" t="n">
-        <v>78967</v>
+        <v>91193</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>769345</v>
+        <v>769413</v>
       </c>
       <c r="R31" t="n">
-        <v>7087087</v>
+        <v>7087074</v>
       </c>
       <c r="S31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4257,7 +4248,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4267,7 +4258,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4314,45 +4305,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125957105</v>
+        <v>125955277</v>
       </c>
       <c r="B32" t="n">
-        <v>91192</v>
+        <v>78968</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>769413</v>
+        <v>769594</v>
       </c>
       <c r="R32" t="n">
-        <v>7087074</v>
+        <v>7087023</v>
       </c>
       <c r="S32" t="n">
         <v>2</v>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4405,11 +4405,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4441,10 +4436,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125955277</v>
+        <v>125957578</v>
       </c>
       <c r="B33" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4471,7 +4466,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4485,13 +4480,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>769594</v>
+        <v>769345</v>
       </c>
       <c r="R33" t="n">
-        <v>7087023</v>
+        <v>7087087</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4520,7 +4515,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4530,7 +4525,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4541,6 +4536,11 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>125956746</v>
       </c>
       <c r="B34" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>125957354</v>
       </c>
       <c r="B35" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2415,7 +2415,7 @@
         <v>125592468</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>125601124</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>125596546</v>
       </c>
       <c r="B22" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>125592263</v>
       </c>
       <c r="B23" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>125599815</v>
       </c>
       <c r="B24" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4178,45 +4178,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125957105</v>
+        <v>125955277</v>
       </c>
       <c r="B31" t="n">
-        <v>91193</v>
+        <v>78968</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>769413</v>
+        <v>769594</v>
       </c>
       <c r="R31" t="n">
-        <v>7087074</v>
+        <v>7087023</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
@@ -4248,7 +4257,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4258,7 +4267,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4269,11 +4278,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4305,54 +4309,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125955277</v>
+        <v>125957105</v>
       </c>
       <c r="B32" t="n">
-        <v>78968</v>
+        <v>91193</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>769594</v>
+        <v>769413</v>
       </c>
       <c r="R32" t="n">
-        <v>7087023</v>
+        <v>7087074</v>
       </c>
       <c r="S32" t="n">
         <v>2</v>
@@ -4384,7 +4379,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4394,7 +4389,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4405,6 +4400,11 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4842,6 +4842,3443 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126034881</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>768925</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7087013</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>Granhögstubbe, knäckt</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126034897</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>769411</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7086946</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre tunn sälg, flera bålar av lunglav</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126034901</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91246</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>768993</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7087062</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies # granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126034893</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>768983</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7087095</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>Död, stående</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies # Död, stående</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126034874</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91193</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>769382</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7087083</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>Granlåga delvis utan bark</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga delvis utan bark</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126034892</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>768979</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7087095</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>Död, stående</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies # Död, stående</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126034899</v>
+      </c>
+      <c r="B42" t="n">
+        <v>56834</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>avledningsbeteende</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>769063</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7087058</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126034867</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91193</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>769351</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7087093</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>granlåga vindfälle mossbevuxen grov</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies # granlåga vindfälle mossbevuxen grov</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126034889</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>768845</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7087079</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Aktiva trämyror</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>Död, stående</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies # Död, stående</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126034875</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91228</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>769232</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7086940</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>Granlåga knäckt äldre mossbevuxen</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga knäckt äldre mossbevuxen</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126034898</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>67</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Sprickporing</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Diplomitoporus crustulinus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Bres.) Domański</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>769524</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7087083</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126034902</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91246</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>769563</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7087014</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies # granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126034878</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>769399</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7086925</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126034871</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91193</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>768896</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7087072</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>Granlåga, knäckt,  tunnare nedsänkt mossa</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga, knäckt,  tunnare nedsänkt mossa</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126034880</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>769558</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7087012</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, lågt ned på stammen</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126034890</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>768927</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7087074</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>Död, stående</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies # Död, stående</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126034872</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91193</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>769400</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7086922</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>Granlåga, knäckt</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga, knäckt</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>126034894</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>768858</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7087093</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>Död, knäckt</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies # Död, knäckt</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>126034869</v>
+      </c>
+      <c r="B54" t="n">
+        <v>91193</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>769400</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7087029</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>granlåga rotvälta</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies # granlåga rotvälta</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>126034877</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91228</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>769560</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7087013</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>Granlåga, knäckt</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga, knäckt</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126034900</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91224</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>768994</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7086995</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>Gran stående</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Picea abies # Gran stående</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>126034896</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>769081</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7087072</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Basen av granen</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126034891</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>768972</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7087057</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>Död, stående</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies # Död, stående</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>126034887</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>768983</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7087100</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Picea abies # Levande</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>126034903</v>
+      </c>
+      <c r="B60" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>768982</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7087094</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>Död gran</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies # Död gran</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>126034870</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91193</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>769323</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7087087</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>Granlåga över bäck</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga över bäck</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>126034888</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>768983</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7087104</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL62" t="inlineStr">
+        <is>
+          <t>Levande</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Picea abies # Levande</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>126034873</v>
+      </c>
+      <c r="B63" t="n">
+        <v>91193</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>768910</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7087060</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>Granlåga, knäckt</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga, knäckt</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126034876</v>
+      </c>
+      <c r="B64" t="n">
+        <v>91228</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>769088</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7087046</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>Granlåga, knäckt, delvis nedsjunken i mossa</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga, knäckt, delvis nedsjunken i mossa</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8279,6 +8279,1090 @@
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>126077588</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98359</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>769260</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7087017</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>126077586</v>
+      </c>
+      <c r="B66" t="n">
+        <v>91232</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>769682</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7087017</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>126077591</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>769239</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7086965</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>126077598</v>
+      </c>
+      <c r="B68" t="n">
+        <v>91250</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>769701</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7086999</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>126077587</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98359</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>769274</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7087024</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>126077589</v>
+      </c>
+      <c r="B70" t="n">
+        <v>98359</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>769261</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7086996</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>126077593</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57597</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>769409</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7086942</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>126077590</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>769228</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7086980</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>126077592</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>769236</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7086947</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>126077585</v>
+      </c>
+      <c r="B74" t="n">
+        <v>91197</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>769715</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7087020</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>126077597</v>
+      </c>
+      <c r="B75" t="n">
+        <v>58326</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>769245</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7087082</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -2415,7 +2415,7 @@
         <v>125592468</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>125601124</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>125596546</v>
       </c>
       <c r="B22" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>125592263</v>
       </c>
       <c r="B23" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>125599815</v>
       </c>
       <c r="B24" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>125956621</v>
       </c>
       <c r="B29" t="n">
-        <v>91224</v>
+        <v>91228</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4178,54 +4178,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125955277</v>
+        <v>125957105</v>
       </c>
       <c r="B31" t="n">
-        <v>78968</v>
+        <v>91197</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>769594</v>
+        <v>769413</v>
       </c>
       <c r="R31" t="n">
-        <v>7087023</v>
+        <v>7087074</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
@@ -4257,7 +4248,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4267,7 +4258,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4278,6 +4269,11 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4309,45 +4305,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125957105</v>
+        <v>125955277</v>
       </c>
       <c r="B32" t="n">
-        <v>91193</v>
+        <v>78972</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>769413</v>
+        <v>769594</v>
       </c>
       <c r="R32" t="n">
-        <v>7087074</v>
+        <v>7087023</v>
       </c>
       <c r="S32" t="n">
         <v>2</v>
@@ -4379,7 +4384,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4389,7 +4394,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4400,11 +4405,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>125957578</v>
       </c>
       <c r="B33" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>125956746</v>
       </c>
       <c r="B34" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>125957354</v>
       </c>
       <c r="B35" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4844,10 +4844,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126034881</v>
+        <v>126034897</v>
       </c>
       <c r="B36" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4855,39 +4855,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>768925</v>
+        <v>769411</v>
       </c>
       <c r="R36" t="n">
-        <v>7087013</v>
+        <v>7086946</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4922,6 +4917,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre tunn sälg, flera bålar av lunglav</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4933,22 +4933,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>Granhögstubbe, knäckt</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4966,10 +4961,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126034897</v>
+        <v>126034901</v>
       </c>
       <c r="B37" t="n">
-        <v>80071</v>
+        <v>91250</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4977,21 +4972,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5001,10 +4996,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>769411</v>
+        <v>768993</v>
       </c>
       <c r="R37" t="n">
-        <v>7086946</v>
+        <v>7087062</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5039,11 +5034,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre tunn sälg, flera bålar av lunglav</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5055,17 +5045,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>granlåga knäckt</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies # granlåga knäckt</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5083,10 +5078,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126034901</v>
+        <v>126034881</v>
       </c>
       <c r="B38" t="n">
-        <v>91246</v>
+        <v>57651</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5094,34 +5089,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>768993</v>
+        <v>768925</v>
       </c>
       <c r="R38" t="n">
-        <v>7087062</v>
+        <v>7087013</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5177,12 +5177,12 @@
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>granlåga knäckt</t>
+          <t>Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga knäckt</t>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5200,50 +5200,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126034893</v>
+        <v>126034874</v>
       </c>
       <c r="B39" t="n">
-        <v>57648</v>
+        <v>91197</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>768983</v>
+        <v>769382</v>
       </c>
       <c r="R39" t="n">
-        <v>7087095</v>
+        <v>7087083</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5299,12 +5294,12 @@
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>Död, stående</t>
+          <t>Granlåga delvis utan bark</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies # Död, stående</t>
+          <t>Picea abies # Granlåga delvis utan bark</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5322,45 +5317,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126034874</v>
+        <v>126034893</v>
       </c>
       <c r="B40" t="n">
-        <v>91193</v>
+        <v>57648</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>769382</v>
+        <v>768983</v>
       </c>
       <c r="R40" t="n">
-        <v>7087083</v>
+        <v>7087095</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>Granlåga delvis utan bark</t>
+          <t>Död, stående</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga delvis utan bark</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5561,54 +5561,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126034899</v>
+        <v>126034867</v>
       </c>
       <c r="B42" t="n">
-        <v>56834</v>
+        <v>91197</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>avledningsbeteende</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>769063</v>
+        <v>769351</v>
       </c>
       <c r="R42" t="n">
-        <v>7087058</v>
+        <v>7087093</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5651,6 +5642,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>granlåga vindfälle mossbevuxen grov</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies # granlåga vindfälle mossbevuxen grov</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5667,45 +5678,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126034867</v>
+        <v>126034899</v>
       </c>
       <c r="B43" t="n">
-        <v>91193</v>
+        <v>56834</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>avledningsbeteende</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>769351</v>
+        <v>769063</v>
       </c>
       <c r="R43" t="n">
-        <v>7087093</v>
+        <v>7087058</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5748,26 +5768,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>granlåga vindfälle mossbevuxen grov</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies # granlåga vindfälle mossbevuxen grov</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5914,7 +5914,7 @@
         <v>126034875</v>
       </c>
       <c r="B45" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>126034898</v>
       </c>
       <c r="B46" t="n">
-        <v>91930</v>
+        <v>91934</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>126034902</v>
       </c>
       <c r="B47" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6374,45 +6374,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126034871</v>
+        <v>126034880</v>
       </c>
       <c r="B49" t="n">
-        <v>91193</v>
+        <v>57651</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>768896</v>
+        <v>769558</v>
       </c>
       <c r="R49" t="n">
-        <v>7087072</v>
+        <v>7087012</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6447,6 +6452,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, lågt ned på stammen</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6466,14 +6476,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL49" t="inlineStr">
-        <is>
-          <t>Granlåga, knäckt,  tunnare nedsänkt mossa</t>
-        </is>
-      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt,  tunnare nedsänkt mossa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6491,50 +6496,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126034880</v>
+        <v>126034871</v>
       </c>
       <c r="B50" t="n">
-        <v>57651</v>
+        <v>91197</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>769558</v>
+        <v>768896</v>
       </c>
       <c r="R50" t="n">
-        <v>7087012</v>
+        <v>7087072</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6569,11 +6569,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, lågt ned på stammen</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6593,9 +6588,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>Granlåga, knäckt,  tunnare nedsänkt mossa</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga, knäckt,  tunnare nedsänkt mossa</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6735,45 +6735,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126034872</v>
+        <v>126034894</v>
       </c>
       <c r="B52" t="n">
-        <v>91193</v>
+        <v>57648</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>769400</v>
+        <v>768858</v>
       </c>
       <c r="R52" t="n">
-        <v>7086922</v>
+        <v>7087093</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6829,12 +6834,12 @@
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt</t>
+          <t>Död, knäckt</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies # Död, knäckt</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6852,10 +6857,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126034894</v>
+        <v>126034877</v>
       </c>
       <c r="B53" t="n">
-        <v>57648</v>
+        <v>91232</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6863,39 +6868,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>768858</v>
+        <v>769560</v>
       </c>
       <c r="R53" t="n">
-        <v>7087093</v>
+        <v>7087013</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6951,12 +6951,12 @@
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>Död, knäckt</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies # Död, knäckt</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6974,10 +6974,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126034869</v>
+        <v>126034872</v>
       </c>
       <c r="B54" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>769400</v>
       </c>
       <c r="R54" t="n">
-        <v>7087029</v>
+        <v>7086922</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7068,12 +7068,12 @@
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>granlåga rotvälta</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga rotvälta</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7091,32 +7091,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126034877</v>
+        <v>126034869</v>
       </c>
       <c r="B55" t="n">
-        <v>91228</v>
+        <v>91197</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>769560</v>
+        <v>769400</v>
       </c>
       <c r="R55" t="n">
-        <v>7087013</v>
+        <v>7087029</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7185,12 +7185,12 @@
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt</t>
+          <t>granlåga rotvälta</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies # granlåga rotvälta</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7208,10 +7208,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126034900</v>
+        <v>126034896</v>
       </c>
       <c r="B56" t="n">
-        <v>91224</v>
+        <v>57648</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7219,34 +7219,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>768994</v>
+        <v>769081</v>
       </c>
       <c r="R56" t="n">
-        <v>7086995</v>
+        <v>7087072</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7281,6 +7286,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Basen av granen</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7300,14 +7310,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL56" t="inlineStr">
-        <is>
-          <t>Gran stående</t>
-        </is>
-      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies # Gran stående</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7325,7 +7330,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126034896</v>
+        <v>126034891</v>
       </c>
       <c r="B57" t="n">
         <v>57648</v>
@@ -7356,7 +7361,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7365,10 +7370,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>769081</v>
+        <v>768972</v>
       </c>
       <c r="R57" t="n">
-        <v>7087072</v>
+        <v>7087057</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7403,11 +7408,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Basen av granen</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7427,9 +7427,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>Död, stående</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7447,10 +7452,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126034891</v>
+        <v>126034900</v>
       </c>
       <c r="B58" t="n">
-        <v>57648</v>
+        <v>91228</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7458,39 +7463,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>768972</v>
+        <v>768994</v>
       </c>
       <c r="R58" t="n">
-        <v>7087057</v>
+        <v>7086995</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>Död, stående</t>
+          <t>Gran stående</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies # Död, stående</t>
+          <t>Picea abies # Gran stående</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7694,7 +7694,7 @@
         <v>126034903</v>
       </c>
       <c r="B60" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>126034870</v>
       </c>
       <c r="B61" t="n">
-        <v>91193</v>
+        <v>91197</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8047,32 +8047,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126034873</v>
+        <v>126034876</v>
       </c>
       <c r="B63" t="n">
-        <v>91193</v>
+        <v>91232</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8082,10 +8082,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>768910</v>
+        <v>769088</v>
       </c>
       <c r="R63" t="n">
-        <v>7087060</v>
+        <v>7087046</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -8141,12 +8141,12 @@
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt</t>
+          <t>Granlåga, knäckt, delvis nedsjunken i mossa</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies # Granlåga, knäckt, delvis nedsjunken i mossa</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8164,32 +8164,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126034876</v>
+        <v>126034873</v>
       </c>
       <c r="B64" t="n">
-        <v>91228</v>
+        <v>91197</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8199,10 +8199,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>769088</v>
+        <v>768910</v>
       </c>
       <c r="R64" t="n">
-        <v>7087046</v>
+        <v>7087060</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8258,12 +8258,12 @@
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt, delvis nedsjunken i mossa</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt, delvis nedsjunken i mossa</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8767,45 +8767,53 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126077589</v>
+        <v>126077593</v>
       </c>
       <c r="B70" t="n">
-        <v>98359</v>
+        <v>57597</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>100067</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>769261</v>
+        <v>769409</v>
       </c>
       <c r="R70" t="n">
-        <v>7086996</v>
+        <v>7086942</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8864,53 +8872,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126077593</v>
+        <v>126077589</v>
       </c>
       <c r="B71" t="n">
-        <v>57597</v>
+        <v>98359</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100067</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>769409</v>
+        <v>769261</v>
       </c>
       <c r="R71" t="n">
-        <v>7086942</v>
+        <v>7086996</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AY83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4961,10 +4961,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126034901</v>
+        <v>126034881</v>
       </c>
       <c r="B37" t="n">
-        <v>91250</v>
+        <v>57651</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4972,34 +4972,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>768993</v>
+        <v>768925</v>
       </c>
       <c r="R37" t="n">
-        <v>7087062</v>
+        <v>7087013</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5055,12 +5060,12 @@
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>granlåga knäckt</t>
+          <t>Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga knäckt</t>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5078,10 +5083,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126034881</v>
+        <v>126034901</v>
       </c>
       <c r="B38" t="n">
-        <v>57651</v>
+        <v>91250</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5089,39 +5094,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>768925</v>
+        <v>768993</v>
       </c>
       <c r="R38" t="n">
-        <v>7087013</v>
+        <v>7087062</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5177,12 +5177,12 @@
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt</t>
+          <t>granlåga knäckt</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
+          <t>Picea abies # granlåga knäckt</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5911,32 +5911,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126034875</v>
+        <v>126034898</v>
       </c>
       <c r="B45" t="n">
-        <v>91232</v>
+        <v>91934</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>769232</v>
+        <v>769524</v>
       </c>
       <c r="R45" t="n">
-        <v>7086940</v>
+        <v>7087083</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5984,6 +5984,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6005,12 +6010,12 @@
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>Granlåga knäckt äldre mossbevuxen</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt äldre mossbevuxen</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6028,32 +6033,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126034898</v>
+        <v>126034875</v>
       </c>
       <c r="B46" t="n">
-        <v>91934</v>
+        <v>91232</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6063,10 +6068,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>769524</v>
+        <v>769232</v>
       </c>
       <c r="R46" t="n">
-        <v>7087083</v>
+        <v>7086940</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6101,11 +6106,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6127,12 +6127,12 @@
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga knäckt äldre mossbevuxen</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlåga knäckt äldre mossbevuxen</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6150,10 +6150,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126034902</v>
+        <v>126034878</v>
       </c>
       <c r="B47" t="n">
-        <v>91250</v>
+        <v>57651</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6161,34 +6161,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>769563</v>
+        <v>769399</v>
       </c>
       <c r="R47" t="n">
-        <v>7087014</v>
+        <v>7086925</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6223,6 +6228,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6231,26 +6241,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies # granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6267,10 +6257,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126034878</v>
+        <v>126034902</v>
       </c>
       <c r="B48" t="n">
-        <v>57651</v>
+        <v>91250</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6278,39 +6268,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>769399</v>
+        <v>769563</v>
       </c>
       <c r="R48" t="n">
-        <v>7086925</v>
+        <v>7087014</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6345,11 +6330,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6358,6 +6338,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies # granlåga knäckt</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6374,50 +6374,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126034880</v>
+        <v>126034871</v>
       </c>
       <c r="B49" t="n">
-        <v>57651</v>
+        <v>91197</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>769558</v>
+        <v>768896</v>
       </c>
       <c r="R49" t="n">
-        <v>7087012</v>
+        <v>7087072</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6452,11 +6447,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, lågt ned på stammen</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6476,9 +6466,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>Granlåga, knäckt,  tunnare nedsänkt mossa</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga, knäckt,  tunnare nedsänkt mossa</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6496,45 +6491,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126034871</v>
+        <v>126034880</v>
       </c>
       <c r="B50" t="n">
-        <v>91197</v>
+        <v>57651</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>768896</v>
+        <v>769558</v>
       </c>
       <c r="R50" t="n">
-        <v>7087072</v>
+        <v>7087012</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6569,6 +6569,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, lågt ned på stammen</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6588,14 +6593,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>Granlåga, knäckt,  tunnare nedsänkt mossa</t>
-        </is>
-      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt,  tunnare nedsänkt mossa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6735,10 +6735,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126034894</v>
+        <v>126034877</v>
       </c>
       <c r="B52" t="n">
-        <v>57648</v>
+        <v>91232</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6746,39 +6746,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>768858</v>
+        <v>769560</v>
       </c>
       <c r="R52" t="n">
-        <v>7087093</v>
+        <v>7087013</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6834,12 +6829,12 @@
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>Död, knäckt</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies # Död, knäckt</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6857,32 +6852,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126034877</v>
+        <v>126034872</v>
       </c>
       <c r="B53" t="n">
-        <v>91232</v>
+        <v>91197</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6892,10 +6887,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>769560</v>
+        <v>769400</v>
       </c>
       <c r="R53" t="n">
-        <v>7087013</v>
+        <v>7086922</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6974,7 +6969,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126034872</v>
+        <v>126034869</v>
       </c>
       <c r="B54" t="n">
         <v>91197</v>
@@ -7012,7 +7007,7 @@
         <v>769400</v>
       </c>
       <c r="R54" t="n">
-        <v>7086922</v>
+        <v>7087029</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7068,12 +7063,12 @@
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt</t>
+          <t>granlåga rotvälta</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies # granlåga rotvälta</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7091,45 +7086,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126034869</v>
+        <v>126034894</v>
       </c>
       <c r="B55" t="n">
-        <v>91197</v>
+        <v>57648</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>769400</v>
+        <v>768858</v>
       </c>
       <c r="R55" t="n">
-        <v>7087029</v>
+        <v>7087093</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7185,12 +7185,12 @@
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>granlåga rotvälta</t>
+          <t>Död, knäckt</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga rotvälta</t>
+          <t>Picea abies # Död, knäckt</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7208,10 +7208,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126034896</v>
+        <v>126034900</v>
       </c>
       <c r="B56" t="n">
-        <v>57648</v>
+        <v>91228</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7219,39 +7219,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>769081</v>
+        <v>768994</v>
       </c>
       <c r="R56" t="n">
-        <v>7087072</v>
+        <v>7086995</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7286,11 +7281,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Basen av granen</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7310,9 +7300,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>Gran stående</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Gran stående</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7330,7 +7325,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126034891</v>
+        <v>126034896</v>
       </c>
       <c r="B57" t="n">
         <v>57648</v>
@@ -7361,7 +7356,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7370,10 +7365,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>768972</v>
+        <v>769081</v>
       </c>
       <c r="R57" t="n">
-        <v>7087057</v>
+        <v>7087072</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7408,6 +7403,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Basen av granen</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7427,14 +7427,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL57" t="inlineStr">
-        <is>
-          <t>Död, stående</t>
-        </is>
-      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies # Död, stående</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7452,10 +7447,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126034900</v>
+        <v>126034891</v>
       </c>
       <c r="B58" t="n">
-        <v>91228</v>
+        <v>57648</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7463,34 +7458,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>768994</v>
+        <v>768972</v>
       </c>
       <c r="R58" t="n">
-        <v>7086995</v>
+        <v>7087057</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>Gran stående</t>
+          <t>Död, stående</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies # Gran stående</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8284,7 +8284,7 @@
         <v>126077588</v>
       </c>
       <c r="B65" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>126077587</v>
       </c>
       <c r="B69" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>126077589</v>
       </c>
       <c r="B71" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9363,6 +9363,878 @@
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>126073254</v>
+      </c>
+      <c r="B76" t="n">
+        <v>98360</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Ultervik, Vb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>769266</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7087014</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>126073253</v>
+      </c>
+      <c r="B77" t="n">
+        <v>98360</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Ultervik, Vb</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>769289</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7087027</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>126131470</v>
+      </c>
+      <c r="B78" t="n">
+        <v>91246</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Mossamyran, Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>769374</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7086933</v>
+      </c>
+      <c r="S78" t="n">
+        <v>2</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>126073252</v>
+      </c>
+      <c r="B79" t="n">
+        <v>80104</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Ultervik, Vb</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>769723</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7086893</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>126073251</v>
+      </c>
+      <c r="B80" t="n">
+        <v>80104</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Ultervik, Vb</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>769759</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7086899</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>126073268</v>
+      </c>
+      <c r="B81" t="n">
+        <v>80110</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Ultervik, Vb</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>769724</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7086894</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>126073262</v>
+      </c>
+      <c r="B82" t="n">
+        <v>78972</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Ultervik, Vb</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>769557</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7086952</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>126073257</v>
+      </c>
+      <c r="B83" t="n">
+        <v>80075</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Ultervik, Vb</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>769727</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7086890</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Maria Wikdahl</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -4844,10 +4844,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126034897</v>
+        <v>126034901</v>
       </c>
       <c r="B36" t="n">
-        <v>80075</v>
+        <v>91250</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4855,21 +4855,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>769411</v>
+        <v>768993</v>
       </c>
       <c r="R36" t="n">
-        <v>7086946</v>
+        <v>7087062</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4917,11 +4917,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre tunn sälg, flera bålar av lunglav</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4933,17 +4928,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>granlåga knäckt</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies # granlåga knäckt</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5083,10 +5083,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126034901</v>
+        <v>126034897</v>
       </c>
       <c r="B38" t="n">
-        <v>91250</v>
+        <v>80075</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5094,21 +5094,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>768993</v>
+        <v>769411</v>
       </c>
       <c r="R38" t="n">
-        <v>7087062</v>
+        <v>7086946</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5156,6 +5156,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre tunn sälg, flera bålar av lunglav</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5167,22 +5172,17 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>granlåga knäckt</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga knäckt</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -6150,10 +6150,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126034878</v>
+        <v>126034902</v>
       </c>
       <c r="B47" t="n">
-        <v>57651</v>
+        <v>91250</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6161,39 +6161,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>769399</v>
+        <v>769563</v>
       </c>
       <c r="R47" t="n">
-        <v>7086925</v>
+        <v>7087014</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6228,11 +6223,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6241,6 +6231,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies # granlåga knäckt</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6257,10 +6267,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126034902</v>
+        <v>126034878</v>
       </c>
       <c r="B48" t="n">
-        <v>91250</v>
+        <v>57651</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6268,34 +6278,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>769563</v>
+        <v>769399</v>
       </c>
       <c r="R48" t="n">
-        <v>7087014</v>
+        <v>7086925</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6330,6 +6345,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6338,26 +6358,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies # granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6374,45 +6374,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126034871</v>
+        <v>126034880</v>
       </c>
       <c r="B49" t="n">
-        <v>91197</v>
+        <v>57651</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>768896</v>
+        <v>769558</v>
       </c>
       <c r="R49" t="n">
-        <v>7087072</v>
+        <v>7087012</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6447,6 +6452,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, lågt ned på stammen</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6466,14 +6476,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL49" t="inlineStr">
-        <is>
-          <t>Granlåga, knäckt,  tunnare nedsänkt mossa</t>
-        </is>
-      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt,  tunnare nedsänkt mossa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6491,50 +6496,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126034880</v>
+        <v>126034871</v>
       </c>
       <c r="B50" t="n">
-        <v>57651</v>
+        <v>91197</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>769558</v>
+        <v>768896</v>
       </c>
       <c r="R50" t="n">
-        <v>7087012</v>
+        <v>7087072</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6569,11 +6569,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, lågt ned på stammen</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6593,9 +6588,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>Granlåga, knäckt,  tunnare nedsänkt mossa</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga, knäckt,  tunnare nedsänkt mossa</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7325,7 +7325,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126034896</v>
+        <v>126034891</v>
       </c>
       <c r="B57" t="n">
         <v>57648</v>
@@ -7356,7 +7356,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7365,10 +7365,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>769081</v>
+        <v>768972</v>
       </c>
       <c r="R57" t="n">
-        <v>7087072</v>
+        <v>7087057</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7403,11 +7403,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Basen av granen</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7427,9 +7422,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>Död, stående</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7447,7 +7447,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126034891</v>
+        <v>126034896</v>
       </c>
       <c r="B58" t="n">
         <v>57648</v>
@@ -7478,7 +7478,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7487,10 +7487,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>768972</v>
+        <v>769081</v>
       </c>
       <c r="R58" t="n">
-        <v>7087057</v>
+        <v>7087072</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7525,6 +7525,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Basen av granen</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7544,14 +7549,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL58" t="inlineStr">
-        <is>
-          <t>Död, stående</t>
-        </is>
-      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies # Död, stående</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -6150,10 +6150,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126034902</v>
+        <v>126034878</v>
       </c>
       <c r="B47" t="n">
-        <v>91250</v>
+        <v>57651</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6161,34 +6161,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>769563</v>
+        <v>769399</v>
       </c>
       <c r="R47" t="n">
-        <v>7087014</v>
+        <v>7086925</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6223,6 +6228,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6231,26 +6241,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies # granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6267,10 +6257,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126034878</v>
+        <v>126034902</v>
       </c>
       <c r="B48" t="n">
-        <v>57651</v>
+        <v>91250</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6278,39 +6268,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>769399</v>
+        <v>769563</v>
       </c>
       <c r="R48" t="n">
-        <v>7086925</v>
+        <v>7087014</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6345,11 +6330,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6358,6 +6338,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies # granlåga knäckt</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6374,50 +6374,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126034880</v>
+        <v>126034871</v>
       </c>
       <c r="B49" t="n">
-        <v>57651</v>
+        <v>91197</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>769558</v>
+        <v>768896</v>
       </c>
       <c r="R49" t="n">
-        <v>7087012</v>
+        <v>7087072</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6452,11 +6447,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, lågt ned på stammen</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6476,9 +6466,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>Granlåga, knäckt,  tunnare nedsänkt mossa</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga, knäckt,  tunnare nedsänkt mossa</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6496,45 +6491,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126034871</v>
+        <v>126034880</v>
       </c>
       <c r="B50" t="n">
-        <v>91197</v>
+        <v>57651</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>768896</v>
+        <v>769558</v>
       </c>
       <c r="R50" t="n">
-        <v>7087072</v>
+        <v>7087012</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6569,6 +6569,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, lågt ned på stammen</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6588,14 +6593,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>Granlåga, knäckt,  tunnare nedsänkt mossa</t>
-        </is>
-      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt,  tunnare nedsänkt mossa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -2151,7 +2151,7 @@
         <v>125595361</v>
       </c>
       <c r="B16" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>125598713</v>
       </c>
       <c r="B17" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>125592468</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>125595152</v>
       </c>
       <c r="B19" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>125601124</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>125598946</v>
       </c>
       <c r="B21" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>125596546</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>125592263</v>
       </c>
       <c r="B23" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>125599815</v>
       </c>
       <c r="B24" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>125599155</v>
       </c>
       <c r="B25" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>125598057</v>
       </c>
       <c r="B26" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>125597783</v>
       </c>
       <c r="B27" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>125958446</v>
       </c>
       <c r="B28" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>125956621</v>
       </c>
       <c r="B29" t="n">
-        <v>91228</v>
+        <v>91230</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>125957531</v>
       </c>
       <c r="B30" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>125957105</v>
       </c>
       <c r="B31" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>125955277</v>
       </c>
       <c r="B32" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>125957578</v>
       </c>
       <c r="B33" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>125956746</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>125957354</v>
       </c>
       <c r="B35" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4844,10 +4844,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126034901</v>
+        <v>126034881</v>
       </c>
       <c r="B36" t="n">
-        <v>91250</v>
+        <v>57652</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4855,34 +4855,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>768993</v>
+        <v>768925</v>
       </c>
       <c r="R36" t="n">
-        <v>7087062</v>
+        <v>7087013</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4938,12 +4943,12 @@
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>granlåga knäckt</t>
+          <t>Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga knäckt</t>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4961,10 +4966,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126034881</v>
+        <v>126034897</v>
       </c>
       <c r="B37" t="n">
-        <v>57651</v>
+        <v>80076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4972,39 +4977,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>768925</v>
+        <v>769411</v>
       </c>
       <c r="R37" t="n">
-        <v>7087013</v>
+        <v>7086946</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5039,6 +5039,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre tunn sälg, flera bålar av lunglav</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5050,22 +5055,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>Granhögstubbe, knäckt</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5083,10 +5083,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126034897</v>
+        <v>126034901</v>
       </c>
       <c r="B38" t="n">
-        <v>80075</v>
+        <v>91252</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5094,21 +5094,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>769411</v>
+        <v>768993</v>
       </c>
       <c r="R38" t="n">
-        <v>7086946</v>
+        <v>7087062</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5156,11 +5156,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre tunn sälg, flera bålar av lunglav</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5172,17 +5167,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>granlåga knäckt</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies # granlåga knäckt</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5200,45 +5200,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126034874</v>
+        <v>126034893</v>
       </c>
       <c r="B39" t="n">
-        <v>91197</v>
+        <v>57649</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>769382</v>
+        <v>768983</v>
       </c>
       <c r="R39" t="n">
-        <v>7087083</v>
+        <v>7087095</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5294,12 +5299,12 @@
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>Granlåga delvis utan bark</t>
+          <t>Död, stående</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga delvis utan bark</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5317,50 +5322,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126034893</v>
+        <v>126034874</v>
       </c>
       <c r="B40" t="n">
-        <v>57648</v>
+        <v>91199</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>768983</v>
+        <v>769382</v>
       </c>
       <c r="R40" t="n">
-        <v>7087095</v>
+        <v>7087083</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>Död, stående</t>
+          <t>Granlåga delvis utan bark</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies # Död, stående</t>
+          <t>Picea abies # Granlåga delvis utan bark</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5442,7 +5442,7 @@
         <v>126034892</v>
       </c>
       <c r="B41" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5561,45 +5561,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126034867</v>
+        <v>126034899</v>
       </c>
       <c r="B42" t="n">
-        <v>91197</v>
+        <v>56835</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>avledningsbeteende</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>769351</v>
+        <v>769063</v>
       </c>
       <c r="R42" t="n">
-        <v>7087093</v>
+        <v>7087058</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5642,26 +5651,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>granlåga vindfälle mossbevuxen grov</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies # granlåga vindfälle mossbevuxen grov</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5678,54 +5667,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126034899</v>
+        <v>126034867</v>
       </c>
       <c r="B43" t="n">
-        <v>56834</v>
+        <v>91199</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>avledningsbeteende</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>769063</v>
+        <v>769351</v>
       </c>
       <c r="R43" t="n">
-        <v>7087058</v>
+        <v>7087093</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5768,6 +5748,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>granlåga vindfälle mossbevuxen grov</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies # granlåga vindfälle mossbevuxen grov</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5787,7 +5787,7 @@
         <v>126034889</v>
       </c>
       <c r="B44" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5911,32 +5911,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126034898</v>
+        <v>126034875</v>
       </c>
       <c r="B45" t="n">
-        <v>91934</v>
+        <v>91234</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>769524</v>
+        <v>769232</v>
       </c>
       <c r="R45" t="n">
-        <v>7087083</v>
+        <v>7086940</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5984,11 +5984,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6010,12 +6005,12 @@
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga knäckt äldre mossbevuxen</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlåga knäckt äldre mossbevuxen</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6033,32 +6028,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126034875</v>
+        <v>126034898</v>
       </c>
       <c r="B46" t="n">
-        <v>91232</v>
+        <v>91936</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6068,10 +6063,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>769232</v>
+        <v>769524</v>
       </c>
       <c r="R46" t="n">
-        <v>7086940</v>
+        <v>7087083</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6106,6 +6101,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6127,12 +6127,12 @@
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>Granlåga knäckt äldre mossbevuxen</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt äldre mossbevuxen</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6153,7 +6153,7 @@
         <v>126034878</v>
       </c>
       <c r="B47" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>126034902</v>
       </c>
       <c r="B48" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6374,45 +6374,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126034871</v>
+        <v>126034890</v>
       </c>
       <c r="B49" t="n">
-        <v>91197</v>
+        <v>57649</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>768896</v>
+        <v>768927</v>
       </c>
       <c r="R49" t="n">
-        <v>7087072</v>
+        <v>7087074</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6468,12 +6473,12 @@
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt,  tunnare nedsänkt mossa</t>
+          <t>Död, stående</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt,  tunnare nedsänkt mossa</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6494,7 +6499,7 @@
         <v>126034880</v>
       </c>
       <c r="B50" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6613,50 +6618,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126034890</v>
+        <v>126034871</v>
       </c>
       <c r="B51" t="n">
-        <v>57648</v>
+        <v>91199</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>768927</v>
+        <v>768896</v>
       </c>
       <c r="R51" t="n">
-        <v>7087074</v>
+        <v>7087072</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6712,12 +6712,12 @@
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>Död, stående</t>
+          <t>Granlåga, knäckt,  tunnare nedsänkt mossa</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies # Död, stående</t>
+          <t>Picea abies # Granlåga, knäckt,  tunnare nedsänkt mossa</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6735,32 +6735,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126034877</v>
+        <v>126034872</v>
       </c>
       <c r="B52" t="n">
-        <v>91232</v>
+        <v>91199</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6770,10 +6770,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>769560</v>
+        <v>769400</v>
       </c>
       <c r="R52" t="n">
-        <v>7087013</v>
+        <v>7086922</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6852,10 +6852,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126034872</v>
+        <v>126034869</v>
       </c>
       <c r="B53" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>769400</v>
       </c>
       <c r="R53" t="n">
-        <v>7086922</v>
+        <v>7087029</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6946,12 +6946,12 @@
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt</t>
+          <t>granlåga rotvälta</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies # granlåga rotvälta</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6969,45 +6969,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126034869</v>
+        <v>126034894</v>
       </c>
       <c r="B54" t="n">
-        <v>91197</v>
+        <v>57649</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>769400</v>
+        <v>768858</v>
       </c>
       <c r="R54" t="n">
-        <v>7087029</v>
+        <v>7087093</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7063,12 +7068,12 @@
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>granlåga rotvälta</t>
+          <t>Död, knäckt</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga rotvälta</t>
+          <t>Picea abies # Död, knäckt</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7086,10 +7091,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126034894</v>
+        <v>126034877</v>
       </c>
       <c r="B55" t="n">
-        <v>57648</v>
+        <v>91234</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7097,39 +7102,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>768858</v>
+        <v>769560</v>
       </c>
       <c r="R55" t="n">
-        <v>7087093</v>
+        <v>7087013</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7185,12 +7185,12 @@
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>Död, knäckt</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies # Död, knäckt</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7211,7 +7211,7 @@
         <v>126034900</v>
       </c>
       <c r="B56" t="n">
-        <v>91228</v>
+        <v>91230</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>126034891</v>
       </c>
       <c r="B57" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>126034896</v>
       </c>
       <c r="B58" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>126034887</v>
       </c>
       <c r="B59" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7691,10 +7691,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126034903</v>
+        <v>126034888</v>
       </c>
       <c r="B60" t="n">
-        <v>78972</v>
+        <v>57649</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7702,34 +7702,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>768982</v>
+        <v>768983</v>
       </c>
       <c r="R60" t="n">
-        <v>7087094</v>
+        <v>7087104</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7785,12 +7790,12 @@
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies # Död gran</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7808,32 +7813,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126034870</v>
+        <v>126034903</v>
       </c>
       <c r="B61" t="n">
-        <v>91197</v>
+        <v>78973</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7843,10 +7848,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>769323</v>
+        <v>768982</v>
       </c>
       <c r="R61" t="n">
-        <v>7087087</v>
+        <v>7087094</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7902,12 +7907,12 @@
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>Granlåga över bäck</t>
+          <t>Död gran</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga över bäck</t>
+          <t>Picea abies # Död gran</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7925,50 +7930,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126034888</v>
+        <v>126034870</v>
       </c>
       <c r="B62" t="n">
-        <v>57648</v>
+        <v>91199</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>768983</v>
+        <v>769323</v>
       </c>
       <c r="R62" t="n">
-        <v>7087104</v>
+        <v>7087087</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granlåga över bäck</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granlåga över bäck</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8050,7 +8050,7 @@
         <v>126034876</v>
       </c>
       <c r="B63" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>126034873</v>
       </c>
       <c r="B64" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>126077588</v>
       </c>
       <c r="B65" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>126077586</v>
       </c>
       <c r="B66" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>126077591</v>
       </c>
       <c r="B67" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>126077598</v>
       </c>
       <c r="B68" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>126077587</v>
       </c>
       <c r="B69" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8767,53 +8767,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126077593</v>
+        <v>126077589</v>
       </c>
       <c r="B70" t="n">
-        <v>57597</v>
+        <v>98362</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100067</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>769409</v>
+        <v>769261</v>
       </c>
       <c r="R70" t="n">
-        <v>7086942</v>
+        <v>7086996</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8872,45 +8864,53 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126077589</v>
+        <v>126077593</v>
       </c>
       <c r="B71" t="n">
-        <v>98360</v>
+        <v>57598</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>100067</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>769261</v>
+        <v>769409</v>
       </c>
       <c r="R71" t="n">
-        <v>7086996</v>
+        <v>7086942</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8972,7 +8972,7 @@
         <v>126077590</v>
       </c>
       <c r="B72" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>126077592</v>
       </c>
       <c r="B73" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>126077585</v>
       </c>
       <c r="B74" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>126077597</v>
       </c>
       <c r="B75" t="n">
-        <v>58326</v>
+        <v>58327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>126073254</v>
       </c>
       <c r="B76" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>126073253</v>
       </c>
       <c r="B77" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>126131470</v>
       </c>
       <c r="B78" t="n">
-        <v>91246</v>
+        <v>91248</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>126073252</v>
       </c>
       <c r="B79" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>126073251</v>
       </c>
       <c r="B80" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>126073268</v>
       </c>
       <c r="B81" t="n">
-        <v>80110</v>
+        <v>80111</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>126073262</v>
       </c>
       <c r="B82" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>126073257</v>
       </c>
       <c r="B83" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -5200,50 +5200,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126034893</v>
+        <v>126034874</v>
       </c>
       <c r="B39" t="n">
-        <v>57649</v>
+        <v>91199</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>768983</v>
+        <v>769382</v>
       </c>
       <c r="R39" t="n">
-        <v>7087095</v>
+        <v>7087083</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5299,12 +5294,12 @@
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>Död, stående</t>
+          <t>Granlåga delvis utan bark</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies # Död, stående</t>
+          <t>Picea abies # Granlåga delvis utan bark</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5322,45 +5317,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126034874</v>
+        <v>126034893</v>
       </c>
       <c r="B40" t="n">
-        <v>91199</v>
+        <v>57649</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>769382</v>
+        <v>768983</v>
       </c>
       <c r="R40" t="n">
-        <v>7087083</v>
+        <v>7087095</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>Granlåga delvis utan bark</t>
+          <t>Död, stående</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga delvis utan bark</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6374,50 +6374,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126034890</v>
+        <v>126034871</v>
       </c>
       <c r="B49" t="n">
-        <v>57649</v>
+        <v>91199</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>768927</v>
+        <v>768896</v>
       </c>
       <c r="R49" t="n">
-        <v>7087074</v>
+        <v>7087072</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6473,12 +6468,12 @@
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>Död, stående</t>
+          <t>Granlåga, knäckt,  tunnare nedsänkt mossa</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies # Död, stående</t>
+          <t>Picea abies # Granlåga, knäckt,  tunnare nedsänkt mossa</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6496,10 +6491,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126034880</v>
+        <v>126034890</v>
       </c>
       <c r="B50" t="n">
-        <v>57652</v>
+        <v>57649</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6507,16 +6502,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6536,10 +6531,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>769558</v>
+        <v>768927</v>
       </c>
       <c r="R50" t="n">
-        <v>7087012</v>
+        <v>7087074</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6574,11 +6569,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, lågt ned på stammen</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6598,9 +6588,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>Död, stående</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6618,45 +6613,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126034871</v>
+        <v>126034880</v>
       </c>
       <c r="B51" t="n">
-        <v>91199</v>
+        <v>57652</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>768896</v>
+        <v>769558</v>
       </c>
       <c r="R51" t="n">
-        <v>7087072</v>
+        <v>7087012</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6691,6 +6691,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, lågt ned på stammen</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6710,14 +6715,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL51" t="inlineStr">
-        <is>
-          <t>Granlåga, knäckt,  tunnare nedsänkt mossa</t>
-        </is>
-      </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt,  tunnare nedsänkt mossa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6735,32 +6735,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126034872</v>
+        <v>126034877</v>
       </c>
       <c r="B52" t="n">
-        <v>91199</v>
+        <v>91234</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6770,10 +6770,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>769400</v>
+        <v>769560</v>
       </c>
       <c r="R52" t="n">
-        <v>7086922</v>
+        <v>7087013</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -7091,32 +7091,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126034877</v>
+        <v>126034872</v>
       </c>
       <c r="B55" t="n">
-        <v>91234</v>
+        <v>91199</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>769560</v>
+        <v>769400</v>
       </c>
       <c r="R55" t="n">
-        <v>7087013</v>
+        <v>7086922</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7208,10 +7208,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126034900</v>
+        <v>126034891</v>
       </c>
       <c r="B56" t="n">
-        <v>91230</v>
+        <v>57649</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7219,34 +7219,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>768994</v>
+        <v>768972</v>
       </c>
       <c r="R56" t="n">
-        <v>7086995</v>
+        <v>7087057</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7302,12 +7307,12 @@
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>Gran stående</t>
+          <t>Död, stående</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies # Gran stående</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7325,7 +7330,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126034891</v>
+        <v>126034896</v>
       </c>
       <c r="B57" t="n">
         <v>57649</v>
@@ -7356,7 +7361,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7365,10 +7370,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>768972</v>
+        <v>769081</v>
       </c>
       <c r="R57" t="n">
-        <v>7087057</v>
+        <v>7087072</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7403,6 +7408,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Basen av granen</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7422,14 +7432,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL57" t="inlineStr">
-        <is>
-          <t>Död, stående</t>
-        </is>
-      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies # Död, stående</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7447,10 +7452,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126034896</v>
+        <v>126034900</v>
       </c>
       <c r="B58" t="n">
-        <v>57649</v>
+        <v>91230</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7458,39 +7463,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>769081</v>
+        <v>768994</v>
       </c>
       <c r="R58" t="n">
-        <v>7087072</v>
+        <v>7086995</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7525,11 +7525,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Basen av granen</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7549,9 +7544,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>Gran stående</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Gran stående</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7691,10 +7691,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126034888</v>
+        <v>126034903</v>
       </c>
       <c r="B60" t="n">
-        <v>57649</v>
+        <v>78973</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7702,39 +7702,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>768983</v>
+        <v>768982</v>
       </c>
       <c r="R60" t="n">
-        <v>7087104</v>
+        <v>7087094</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7790,12 +7785,12 @@
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Död gran</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Död gran</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7813,32 +7808,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126034903</v>
+        <v>126034870</v>
       </c>
       <c r="B61" t="n">
-        <v>78973</v>
+        <v>91199</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7848,10 +7843,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>768982</v>
+        <v>769323</v>
       </c>
       <c r="R61" t="n">
-        <v>7087094</v>
+        <v>7087087</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7907,12 +7902,12 @@
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>Granlåga över bäck</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies # Död gran</t>
+          <t>Picea abies # Granlåga över bäck</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7930,45 +7925,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126034870</v>
+        <v>126034888</v>
       </c>
       <c r="B62" t="n">
-        <v>91199</v>
+        <v>57649</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>769323</v>
+        <v>768983</v>
       </c>
       <c r="R62" t="n">
-        <v>7087087</v>
+        <v>7087104</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>Granlåga över bäck</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga över bäck</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -3913,7 +3913,7 @@
         <v>125956621</v>
       </c>
       <c r="B29" t="n">
-        <v>91230</v>
+        <v>91232</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>125957105</v>
       </c>
       <c r="B31" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4844,10 +4844,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126034881</v>
+        <v>126034901</v>
       </c>
       <c r="B36" t="n">
-        <v>57652</v>
+        <v>91254</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4855,39 +4855,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>768925</v>
+        <v>768993</v>
       </c>
       <c r="R36" t="n">
-        <v>7087013</v>
+        <v>7087062</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4943,12 +4938,12 @@
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt</t>
+          <t>granlåga knäckt</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
+          <t>Picea abies # granlåga knäckt</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4966,10 +4961,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126034897</v>
+        <v>126034881</v>
       </c>
       <c r="B37" t="n">
-        <v>80076</v>
+        <v>57652</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4977,34 +4972,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>769411</v>
+        <v>768925</v>
       </c>
       <c r="R37" t="n">
-        <v>7086946</v>
+        <v>7087013</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5039,11 +5039,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre tunn sälg, flera bålar av lunglav</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5055,17 +5050,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5083,10 +5083,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126034901</v>
+        <v>126034897</v>
       </c>
       <c r="B38" t="n">
-        <v>91252</v>
+        <v>80076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5094,21 +5094,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>768993</v>
+        <v>769411</v>
       </c>
       <c r="R38" t="n">
-        <v>7087062</v>
+        <v>7086946</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5156,6 +5156,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre tunn sälg, flera bålar av lunglav</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5167,22 +5172,17 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>granlåga knäckt</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga knäckt</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5203,7 +5203,7 @@
         <v>126034874</v>
       </c>
       <c r="B39" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5561,54 +5561,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126034899</v>
+        <v>126034867</v>
       </c>
       <c r="B42" t="n">
-        <v>56835</v>
+        <v>91201</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>avledningsbeteende</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>769063</v>
+        <v>769351</v>
       </c>
       <c r="R42" t="n">
-        <v>7087058</v>
+        <v>7087093</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5651,6 +5642,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>granlåga vindfälle mossbevuxen grov</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies # granlåga vindfälle mossbevuxen grov</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5667,45 +5678,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126034867</v>
+        <v>126034899</v>
       </c>
       <c r="B43" t="n">
-        <v>91199</v>
+        <v>56835</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>avledningsbeteende</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>769351</v>
+        <v>769063</v>
       </c>
       <c r="R43" t="n">
-        <v>7087093</v>
+        <v>7087058</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5748,26 +5768,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>granlåga vindfälle mossbevuxen grov</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies # granlåga vindfälle mossbevuxen grov</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5911,32 +5911,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126034875</v>
+        <v>126034898</v>
       </c>
       <c r="B45" t="n">
-        <v>91234</v>
+        <v>91938</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>769232</v>
+        <v>769524</v>
       </c>
       <c r="R45" t="n">
-        <v>7086940</v>
+        <v>7087083</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5984,6 +5984,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6005,12 +6010,12 @@
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>Granlåga knäckt äldre mossbevuxen</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt äldre mossbevuxen</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6028,32 +6033,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126034898</v>
+        <v>126034875</v>
       </c>
       <c r="B46" t="n">
-        <v>91936</v>
+        <v>91236</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6063,10 +6068,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>769524</v>
+        <v>769232</v>
       </c>
       <c r="R46" t="n">
-        <v>7087083</v>
+        <v>7086940</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6101,11 +6106,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6127,12 +6127,12 @@
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga knäckt äldre mossbevuxen</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlåga knäckt äldre mossbevuxen</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6150,10 +6150,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126034878</v>
+        <v>126034902</v>
       </c>
       <c r="B47" t="n">
-        <v>57652</v>
+        <v>91254</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6161,39 +6161,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>769399</v>
+        <v>769563</v>
       </c>
       <c r="R47" t="n">
-        <v>7086925</v>
+        <v>7087014</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6228,11 +6223,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6241,6 +6231,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies # granlåga knäckt</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6257,10 +6267,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126034902</v>
+        <v>126034878</v>
       </c>
       <c r="B48" t="n">
-        <v>91252</v>
+        <v>57652</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6268,34 +6278,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>769563</v>
+        <v>769399</v>
       </c>
       <c r="R48" t="n">
-        <v>7087014</v>
+        <v>7086925</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6330,6 +6345,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6338,26 +6358,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies # granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6377,7 +6377,7 @@
         <v>126034871</v>
       </c>
       <c r="B49" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>126034877</v>
       </c>
       <c r="B52" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6852,45 +6852,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126034869</v>
+        <v>126034894</v>
       </c>
       <c r="B53" t="n">
-        <v>91199</v>
+        <v>57649</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>769400</v>
+        <v>768858</v>
       </c>
       <c r="R53" t="n">
-        <v>7087029</v>
+        <v>7087093</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6946,12 +6951,12 @@
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>granlåga rotvälta</t>
+          <t>Död, knäckt</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga rotvälta</t>
+          <t>Picea abies # Död, knäckt</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6969,50 +6974,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126034894</v>
+        <v>126034872</v>
       </c>
       <c r="B54" t="n">
-        <v>57649</v>
+        <v>91201</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>768858</v>
+        <v>769400</v>
       </c>
       <c r="R54" t="n">
-        <v>7087093</v>
+        <v>7086922</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7068,12 +7068,12 @@
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>Död, knäckt</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies # Död, knäckt</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7091,10 +7091,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126034872</v>
+        <v>126034869</v>
       </c>
       <c r="B55" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>769400</v>
       </c>
       <c r="R55" t="n">
-        <v>7086922</v>
+        <v>7087029</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7185,12 +7185,12 @@
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt</t>
+          <t>granlåga rotvälta</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies # granlåga rotvälta</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7208,10 +7208,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126034891</v>
+        <v>126034900</v>
       </c>
       <c r="B56" t="n">
-        <v>57649</v>
+        <v>91232</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7219,39 +7219,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>768972</v>
+        <v>768994</v>
       </c>
       <c r="R56" t="n">
-        <v>7087057</v>
+        <v>7086995</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7307,12 +7302,12 @@
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>Död, stående</t>
+          <t>Gran stående</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies # Död, stående</t>
+          <t>Picea abies # Gran stående</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7452,10 +7447,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126034900</v>
+        <v>126034891</v>
       </c>
       <c r="B58" t="n">
-        <v>91230</v>
+        <v>57649</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7463,34 +7458,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>768994</v>
+        <v>768972</v>
       </c>
       <c r="R58" t="n">
-        <v>7086995</v>
+        <v>7087057</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>Gran stående</t>
+          <t>Död, stående</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies # Gran stående</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7691,32 +7691,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126034903</v>
+        <v>126034870</v>
       </c>
       <c r="B60" t="n">
-        <v>78973</v>
+        <v>91201</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7726,10 +7726,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>768982</v>
+        <v>769323</v>
       </c>
       <c r="R60" t="n">
-        <v>7087094</v>
+        <v>7087087</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>Granlåga över bäck</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies # Död gran</t>
+          <t>Picea abies # Granlåga över bäck</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7808,32 +7808,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126034870</v>
+        <v>126034903</v>
       </c>
       <c r="B61" t="n">
-        <v>91199</v>
+        <v>78973</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7843,10 +7843,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>769323</v>
+        <v>768982</v>
       </c>
       <c r="R61" t="n">
-        <v>7087087</v>
+        <v>7087094</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7902,12 +7902,12 @@
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>Granlåga över bäck</t>
+          <t>Död gran</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga över bäck</t>
+          <t>Picea abies # Död gran</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8050,7 +8050,7 @@
         <v>126034876</v>
       </c>
       <c r="B63" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>126034873</v>
       </c>
       <c r="B64" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>126077588</v>
       </c>
       <c r="B65" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>126077586</v>
       </c>
       <c r="B66" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>126077598</v>
       </c>
       <c r="B68" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>126077587</v>
       </c>
       <c r="B69" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8767,45 +8767,53 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126077589</v>
+        <v>126077593</v>
       </c>
       <c r="B70" t="n">
-        <v>98362</v>
+        <v>57598</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>100067</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>769261</v>
+        <v>769409</v>
       </c>
       <c r="R70" t="n">
-        <v>7086996</v>
+        <v>7086942</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8864,53 +8872,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126077593</v>
+        <v>126077589</v>
       </c>
       <c r="B71" t="n">
-        <v>57598</v>
+        <v>98364</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100067</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>769409</v>
+        <v>769261</v>
       </c>
       <c r="R71" t="n">
-        <v>7086942</v>
+        <v>7086996</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9166,7 +9166,7 @@
         <v>126077585</v>
       </c>
       <c r="B74" t="n">
-        <v>91199</v>
+        <v>91201</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>126073254</v>
       </c>
       <c r="B76" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>126073253</v>
       </c>
       <c r="B77" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>126131470</v>
       </c>
       <c r="B78" t="n">
-        <v>91248</v>
+        <v>91250</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -4961,10 +4961,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126034881</v>
+        <v>126034897</v>
       </c>
       <c r="B37" t="n">
-        <v>57652</v>
+        <v>80076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4972,39 +4972,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>768925</v>
+        <v>769411</v>
       </c>
       <c r="R37" t="n">
-        <v>7087013</v>
+        <v>7086946</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5039,6 +5034,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre tunn sälg, flera bålar av lunglav</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5050,22 +5050,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>Granhögstubbe, knäckt</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5083,10 +5078,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126034897</v>
+        <v>126034881</v>
       </c>
       <c r="B38" t="n">
-        <v>80076</v>
+        <v>57652</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5094,34 +5089,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>769411</v>
+        <v>768925</v>
       </c>
       <c r="R38" t="n">
-        <v>7086946</v>
+        <v>7087013</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5156,11 +5156,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre tunn sälg, flera bålar av lunglav</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5172,17 +5167,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5911,32 +5911,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126034898</v>
+        <v>126034875</v>
       </c>
       <c r="B45" t="n">
-        <v>91938</v>
+        <v>91236</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>769524</v>
+        <v>769232</v>
       </c>
       <c r="R45" t="n">
-        <v>7087083</v>
+        <v>7086940</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5984,11 +5984,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6010,12 +6005,12 @@
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga knäckt äldre mossbevuxen</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlåga knäckt äldre mossbevuxen</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6033,32 +6028,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126034875</v>
+        <v>126034898</v>
       </c>
       <c r="B46" t="n">
-        <v>91236</v>
+        <v>91938</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6068,10 +6063,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>769232</v>
+        <v>769524</v>
       </c>
       <c r="R46" t="n">
-        <v>7086940</v>
+        <v>7087083</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6106,6 +6101,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6127,12 +6127,12 @@
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>Granlåga knäckt äldre mossbevuxen</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt äldre mossbevuxen</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -7691,32 +7691,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126034870</v>
+        <v>126034903</v>
       </c>
       <c r="B60" t="n">
-        <v>91201</v>
+        <v>78973</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7726,10 +7726,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>769323</v>
+        <v>768982</v>
       </c>
       <c r="R60" t="n">
-        <v>7087087</v>
+        <v>7087094</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>Granlåga över bäck</t>
+          <t>Död gran</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga över bäck</t>
+          <t>Picea abies # Död gran</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7808,32 +7808,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126034903</v>
+        <v>126034870</v>
       </c>
       <c r="B61" t="n">
-        <v>78973</v>
+        <v>91201</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7843,10 +7843,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>768982</v>
+        <v>769323</v>
       </c>
       <c r="R61" t="n">
-        <v>7087094</v>
+        <v>7087087</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7902,12 +7902,12 @@
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>Granlåga över bäck</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies # Död gran</t>
+          <t>Picea abies # Granlåga över bäck</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -3913,7 +3913,7 @@
         <v>125956621</v>
       </c>
       <c r="B29" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>125957105</v>
       </c>
       <c r="B31" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>126034901</v>
       </c>
       <c r="B36" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>126034874</v>
       </c>
       <c r="B39" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>126034867</v>
       </c>
       <c r="B42" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>126034875</v>
       </c>
       <c r="B45" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>126034898</v>
       </c>
       <c r="B46" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>126034902</v>
       </c>
       <c r="B47" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>126034871</v>
       </c>
       <c r="B49" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>126034877</v>
       </c>
       <c r="B52" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6852,50 +6852,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126034894</v>
+        <v>126034872</v>
       </c>
       <c r="B53" t="n">
-        <v>57649</v>
+        <v>91203</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>768858</v>
+        <v>769400</v>
       </c>
       <c r="R53" t="n">
-        <v>7087093</v>
+        <v>7086922</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6951,12 +6946,12 @@
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>Död, knäckt</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies # Död, knäckt</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6974,10 +6969,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126034872</v>
+        <v>126034869</v>
       </c>
       <c r="B54" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7012,7 +7007,7 @@
         <v>769400</v>
       </c>
       <c r="R54" t="n">
-        <v>7086922</v>
+        <v>7087029</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7068,12 +7063,12 @@
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt</t>
+          <t>granlåga rotvälta</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies # granlåga rotvälta</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7091,45 +7086,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126034869</v>
+        <v>126034894</v>
       </c>
       <c r="B55" t="n">
-        <v>91201</v>
+        <v>57649</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>769400</v>
+        <v>768858</v>
       </c>
       <c r="R55" t="n">
-        <v>7087029</v>
+        <v>7087093</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7185,12 +7185,12 @@
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>granlåga rotvälta</t>
+          <t>Död, knäckt</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga rotvälta</t>
+          <t>Picea abies # Död, knäckt</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7208,10 +7208,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126034900</v>
+        <v>126034896</v>
       </c>
       <c r="B56" t="n">
-        <v>91232</v>
+        <v>57649</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7219,34 +7219,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>768994</v>
+        <v>769081</v>
       </c>
       <c r="R56" t="n">
-        <v>7086995</v>
+        <v>7087072</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7281,6 +7286,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Basen av granen</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7300,14 +7310,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL56" t="inlineStr">
-        <is>
-          <t>Gran stående</t>
-        </is>
-      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies # Gran stående</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7325,7 +7330,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126034896</v>
+        <v>126034891</v>
       </c>
       <c r="B57" t="n">
         <v>57649</v>
@@ -7356,7 +7361,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7365,10 +7370,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>769081</v>
+        <v>768972</v>
       </c>
       <c r="R57" t="n">
-        <v>7087072</v>
+        <v>7087057</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7403,11 +7408,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Basen av granen</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7427,9 +7427,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>Död, stående</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7447,10 +7452,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126034891</v>
+        <v>126034900</v>
       </c>
       <c r="B58" t="n">
-        <v>57649</v>
+        <v>91234</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7458,39 +7463,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>768972</v>
+        <v>768994</v>
       </c>
       <c r="R58" t="n">
-        <v>7087057</v>
+        <v>7086995</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>Död, stående</t>
+          <t>Gran stående</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies # Död, stående</t>
+          <t>Picea abies # Gran stående</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7811,7 +7811,7 @@
         <v>126034870</v>
       </c>
       <c r="B61" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8047,32 +8047,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126034876</v>
+        <v>126034873</v>
       </c>
       <c r="B63" t="n">
-        <v>91236</v>
+        <v>91203</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8082,10 +8082,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>769088</v>
+        <v>768910</v>
       </c>
       <c r="R63" t="n">
-        <v>7087046</v>
+        <v>7087060</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -8141,12 +8141,12 @@
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt, delvis nedsjunken i mossa</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt, delvis nedsjunken i mossa</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8164,32 +8164,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126034873</v>
+        <v>126034876</v>
       </c>
       <c r="B64" t="n">
-        <v>91201</v>
+        <v>91238</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8199,10 +8199,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>768910</v>
+        <v>769088</v>
       </c>
       <c r="R64" t="n">
-        <v>7087060</v>
+        <v>7087046</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8258,12 +8258,12 @@
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt</t>
+          <t>Granlåga, knäckt, delvis nedsjunken i mossa</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies # Granlåga, knäckt, delvis nedsjunken i mossa</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8284,7 +8284,7 @@
         <v>126077588</v>
       </c>
       <c r="B65" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>126077586</v>
       </c>
       <c r="B66" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>126077598</v>
       </c>
       <c r="B68" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>126077587</v>
       </c>
       <c r="B69" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>126077589</v>
       </c>
       <c r="B71" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>126077585</v>
       </c>
       <c r="B74" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>126073254</v>
       </c>
       <c r="B76" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>126073253</v>
       </c>
       <c r="B77" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>126131470</v>
       </c>
       <c r="B78" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -4844,10 +4844,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126034901</v>
+        <v>126034897</v>
       </c>
       <c r="B36" t="n">
-        <v>91256</v>
+        <v>80076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4855,21 +4855,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>768993</v>
+        <v>769411</v>
       </c>
       <c r="R36" t="n">
-        <v>7087062</v>
+        <v>7086946</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4917,6 +4917,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre tunn sälg, flera bålar av lunglav</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4928,22 +4933,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>granlåga knäckt</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga knäckt</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126034897</v>
+        <v>126034901</v>
       </c>
       <c r="B37" t="n">
-        <v>80076</v>
+        <v>91256</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4972,21 +4972,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4996,10 +4996,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>769411</v>
+        <v>768993</v>
       </c>
       <c r="R37" t="n">
-        <v>7086946</v>
+        <v>7087062</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5034,11 +5034,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre tunn sälg, flera bålar av lunglav</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5050,17 +5045,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>granlåga knäckt</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies # granlåga knäckt</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -3621,7 +3621,7 @@
         <v>125597783</v>
       </c>
       <c r="B27" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>125958446</v>
       </c>
       <c r="B28" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>125956621</v>
       </c>
       <c r="B29" t="n">
-        <v>91234</v>
+        <v>91238</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>125957531</v>
       </c>
       <c r="B30" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4178,45 +4178,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125957105</v>
+        <v>125955277</v>
       </c>
       <c r="B31" t="n">
-        <v>91203</v>
+        <v>78977</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>769413</v>
+        <v>769594</v>
       </c>
       <c r="R31" t="n">
-        <v>7087074</v>
+        <v>7087023</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
@@ -4248,7 +4257,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4258,7 +4267,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4269,11 +4278,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4305,54 +4309,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125955277</v>
+        <v>125957105</v>
       </c>
       <c r="B32" t="n">
-        <v>78973</v>
+        <v>91207</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>769594</v>
+        <v>769413</v>
       </c>
       <c r="R32" t="n">
-        <v>7087023</v>
+        <v>7087074</v>
       </c>
       <c r="S32" t="n">
         <v>2</v>
@@ -4384,7 +4379,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4394,7 +4389,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4405,6 +4400,11 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>125957578</v>
       </c>
       <c r="B33" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>125956746</v>
       </c>
       <c r="B34" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>125957354</v>
       </c>
       <c r="B35" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>126034897</v>
       </c>
       <c r="B36" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4961,10 +4961,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126034901</v>
+        <v>126034881</v>
       </c>
       <c r="B37" t="n">
-        <v>91256</v>
+        <v>57656</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4972,34 +4972,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>768993</v>
+        <v>768925</v>
       </c>
       <c r="R37" t="n">
-        <v>7087062</v>
+        <v>7087013</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5055,12 +5060,12 @@
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>granlåga knäckt</t>
+          <t>Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga knäckt</t>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5078,10 +5083,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126034881</v>
+        <v>126034901</v>
       </c>
       <c r="B38" t="n">
-        <v>57652</v>
+        <v>91260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5089,39 +5094,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>768925</v>
+        <v>768993</v>
       </c>
       <c r="R38" t="n">
-        <v>7087013</v>
+        <v>7087062</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5177,12 +5177,12 @@
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt</t>
+          <t>granlåga knäckt</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
+          <t>Picea abies # granlåga knäckt</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5200,45 +5200,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126034874</v>
+        <v>126034893</v>
       </c>
       <c r="B39" t="n">
-        <v>91203</v>
+        <v>57653</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>769382</v>
+        <v>768983</v>
       </c>
       <c r="R39" t="n">
-        <v>7087083</v>
+        <v>7087095</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5294,12 +5299,12 @@
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>Granlåga delvis utan bark</t>
+          <t>Död, stående</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga delvis utan bark</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5317,50 +5322,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126034893</v>
+        <v>126034874</v>
       </c>
       <c r="B40" t="n">
-        <v>57649</v>
+        <v>91207</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>768983</v>
+        <v>769382</v>
       </c>
       <c r="R40" t="n">
-        <v>7087095</v>
+        <v>7087083</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>Död, stående</t>
+          <t>Granlåga delvis utan bark</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies # Död, stående</t>
+          <t>Picea abies # Granlåga delvis utan bark</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5442,7 +5442,7 @@
         <v>126034892</v>
       </c>
       <c r="B41" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>126034867</v>
       </c>
       <c r="B42" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>126034899</v>
       </c>
       <c r="B43" t="n">
-        <v>56835</v>
+        <v>56839</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>126034889</v>
       </c>
       <c r="B44" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5911,32 +5911,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126034875</v>
+        <v>126034898</v>
       </c>
       <c r="B45" t="n">
-        <v>91238</v>
+        <v>91944</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>769232</v>
+        <v>769524</v>
       </c>
       <c r="R45" t="n">
-        <v>7086940</v>
+        <v>7087083</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5984,6 +5984,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6005,12 +6010,12 @@
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>Granlåga knäckt äldre mossbevuxen</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt äldre mossbevuxen</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6028,32 +6033,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126034898</v>
+        <v>126034875</v>
       </c>
       <c r="B46" t="n">
-        <v>91940</v>
+        <v>91242</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6063,10 +6068,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>769524</v>
+        <v>769232</v>
       </c>
       <c r="R46" t="n">
-        <v>7087083</v>
+        <v>7086940</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6101,11 +6106,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6127,12 +6127,12 @@
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga knäckt äldre mossbevuxen</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlåga knäckt äldre mossbevuxen</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6153,7 +6153,7 @@
         <v>126034902</v>
       </c>
       <c r="B47" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>126034878</v>
       </c>
       <c r="B48" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6374,45 +6374,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126034871</v>
+        <v>126034890</v>
       </c>
       <c r="B49" t="n">
-        <v>91203</v>
+        <v>57653</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>768896</v>
+        <v>768927</v>
       </c>
       <c r="R49" t="n">
-        <v>7087072</v>
+        <v>7087074</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6468,12 +6473,12 @@
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt,  tunnare nedsänkt mossa</t>
+          <t>Död, stående</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt,  tunnare nedsänkt mossa</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6491,50 +6496,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126034890</v>
+        <v>126034871</v>
       </c>
       <c r="B50" t="n">
-        <v>57649</v>
+        <v>91207</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>768927</v>
+        <v>768896</v>
       </c>
       <c r="R50" t="n">
-        <v>7087074</v>
+        <v>7087072</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6590,12 +6590,12 @@
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>Död, stående</t>
+          <t>Granlåga, knäckt,  tunnare nedsänkt mossa</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies # Död, stående</t>
+          <t>Picea abies # Granlåga, knäckt,  tunnare nedsänkt mossa</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6616,7 +6616,7 @@
         <v>126034880</v>
       </c>
       <c r="B51" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6735,10 +6735,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126034877</v>
+        <v>126034894</v>
       </c>
       <c r="B52" t="n">
-        <v>91238</v>
+        <v>57653</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6746,34 +6746,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>769560</v>
+        <v>768858</v>
       </c>
       <c r="R52" t="n">
-        <v>7087013</v>
+        <v>7087093</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6829,12 +6834,12 @@
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt</t>
+          <t>Död, knäckt</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies # Död, knäckt</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6855,7 +6860,7 @@
         <v>126034872</v>
       </c>
       <c r="B53" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6972,7 +6977,7 @@
         <v>126034869</v>
       </c>
       <c r="B54" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7086,10 +7091,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126034894</v>
+        <v>126034877</v>
       </c>
       <c r="B55" t="n">
-        <v>57649</v>
+        <v>91242</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7097,39 +7102,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>768858</v>
+        <v>769560</v>
       </c>
       <c r="R55" t="n">
-        <v>7087093</v>
+        <v>7087013</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7185,12 +7185,12 @@
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>Död, knäckt</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies # Död, knäckt</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7208,10 +7208,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126034896</v>
+        <v>126034891</v>
       </c>
       <c r="B56" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7248,10 +7248,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>769081</v>
+        <v>768972</v>
       </c>
       <c r="R56" t="n">
-        <v>7087072</v>
+        <v>7087057</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7286,11 +7286,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Basen av granen</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7310,9 +7305,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>Död, stående</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7330,10 +7330,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126034891</v>
+        <v>126034900</v>
       </c>
       <c r="B57" t="n">
-        <v>57649</v>
+        <v>91238</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7341,39 +7341,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>768972</v>
+        <v>768994</v>
       </c>
       <c r="R57" t="n">
-        <v>7087057</v>
+        <v>7086995</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7429,12 +7424,12 @@
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>Död, stående</t>
+          <t>Gran stående</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies # Död, stående</t>
+          <t>Picea abies # Gran stående</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7452,10 +7447,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126034900</v>
+        <v>126034896</v>
       </c>
       <c r="B58" t="n">
-        <v>91234</v>
+        <v>57653</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7463,34 +7458,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>768994</v>
+        <v>769081</v>
       </c>
       <c r="R58" t="n">
-        <v>7086995</v>
+        <v>7087072</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7525,6 +7525,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Basen av granen</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7544,14 +7549,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL58" t="inlineStr">
-        <is>
-          <t>Gran stående</t>
-        </is>
-      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies # Gran stående</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7572,7 +7572,7 @@
         <v>126034887</v>
       </c>
       <c r="B59" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7691,10 +7691,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126034903</v>
+        <v>126034888</v>
       </c>
       <c r="B60" t="n">
-        <v>78973</v>
+        <v>57653</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7702,34 +7702,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>768982</v>
+        <v>768983</v>
       </c>
       <c r="R60" t="n">
-        <v>7087094</v>
+        <v>7087104</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7785,12 +7790,12 @@
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies # Död gran</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7808,32 +7813,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126034870</v>
+        <v>126034903</v>
       </c>
       <c r="B61" t="n">
-        <v>91203</v>
+        <v>78977</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7843,10 +7848,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>769323</v>
+        <v>768982</v>
       </c>
       <c r="R61" t="n">
-        <v>7087087</v>
+        <v>7087094</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7902,12 +7907,12 @@
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>Granlåga över bäck</t>
+          <t>Död gran</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga över bäck</t>
+          <t>Picea abies # Död gran</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7925,50 +7930,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126034888</v>
+        <v>126034870</v>
       </c>
       <c r="B62" t="n">
-        <v>57649</v>
+        <v>91207</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>768983</v>
+        <v>769323</v>
       </c>
       <c r="R62" t="n">
-        <v>7087104</v>
+        <v>7087087</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granlåga över bäck</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granlåga över bäck</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8050,7 +8050,7 @@
         <v>126034873</v>
       </c>
       <c r="B63" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>126034876</v>
       </c>
       <c r="B64" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>126077588</v>
       </c>
       <c r="B65" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>126077586</v>
       </c>
       <c r="B66" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>126077591</v>
       </c>
       <c r="B67" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>126077598</v>
       </c>
       <c r="B68" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>126077587</v>
       </c>
       <c r="B69" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>126077593</v>
       </c>
       <c r="B70" t="n">
-        <v>57598</v>
+        <v>57602</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>126077589</v>
       </c>
       <c r="B71" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>126077590</v>
       </c>
       <c r="B72" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>126077592</v>
       </c>
       <c r="B73" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>126077585</v>
       </c>
       <c r="B74" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>126077597</v>
       </c>
       <c r="B75" t="n">
-        <v>58327</v>
+        <v>58331</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>126073254</v>
       </c>
       <c r="B76" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>126073253</v>
       </c>
       <c r="B77" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>126131470</v>
       </c>
       <c r="B78" t="n">
-        <v>91252</v>
+        <v>91256</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>126073252</v>
       </c>
       <c r="B79" t="n">
-        <v>80105</v>
+        <v>80109</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>126073251</v>
       </c>
       <c r="B80" t="n">
-        <v>80105</v>
+        <v>80109</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>126073268</v>
       </c>
       <c r="B81" t="n">
-        <v>80111</v>
+        <v>80115</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>126073262</v>
       </c>
       <c r="B82" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>126073257</v>
       </c>
       <c r="B83" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -5911,32 +5911,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126034898</v>
+        <v>126034875</v>
       </c>
       <c r="B45" t="n">
-        <v>91944</v>
+        <v>91242</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>769524</v>
+        <v>769232</v>
       </c>
       <c r="R45" t="n">
-        <v>7087083</v>
+        <v>7086940</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5984,11 +5984,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6010,12 +6005,12 @@
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga knäckt äldre mossbevuxen</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlåga knäckt äldre mossbevuxen</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6033,32 +6028,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126034875</v>
+        <v>126034898</v>
       </c>
       <c r="B46" t="n">
-        <v>91242</v>
+        <v>91944</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6068,10 +6063,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>769232</v>
+        <v>769524</v>
       </c>
       <c r="R46" t="n">
-        <v>7086940</v>
+        <v>7087083</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6106,6 +6101,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6127,12 +6127,12 @@
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>Granlåga knäckt äldre mossbevuxen</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt äldre mossbevuxen</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6150,10 +6150,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126034902</v>
+        <v>126034878</v>
       </c>
       <c r="B47" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6161,34 +6161,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>769563</v>
+        <v>769399</v>
       </c>
       <c r="R47" t="n">
-        <v>7087014</v>
+        <v>7086925</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6223,6 +6228,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6231,26 +6241,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies # granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6267,10 +6257,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126034878</v>
+        <v>126034902</v>
       </c>
       <c r="B48" t="n">
-        <v>57656</v>
+        <v>91260</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6278,39 +6268,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>769399</v>
+        <v>769563</v>
       </c>
       <c r="R48" t="n">
-        <v>7086925</v>
+        <v>7087014</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6345,11 +6330,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6358,6 +6338,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies # granlåga knäckt</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6374,50 +6374,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126034890</v>
+        <v>126034871</v>
       </c>
       <c r="B49" t="n">
-        <v>57653</v>
+        <v>91207</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>768927</v>
+        <v>768896</v>
       </c>
       <c r="R49" t="n">
-        <v>7087074</v>
+        <v>7087072</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6473,12 +6468,12 @@
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>Död, stående</t>
+          <t>Granlåga, knäckt,  tunnare nedsänkt mossa</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies # Död, stående</t>
+          <t>Picea abies # Granlåga, knäckt,  tunnare nedsänkt mossa</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6496,45 +6491,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126034871</v>
+        <v>126034890</v>
       </c>
       <c r="B50" t="n">
-        <v>91207</v>
+        <v>57653</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>768896</v>
+        <v>768927</v>
       </c>
       <c r="R50" t="n">
-        <v>7087072</v>
+        <v>7087074</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6590,12 +6590,12 @@
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt,  tunnare nedsänkt mossa</t>
+          <t>Död, stående</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt,  tunnare nedsänkt mossa</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6735,50 +6735,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126034894</v>
+        <v>126034872</v>
       </c>
       <c r="B52" t="n">
-        <v>57653</v>
+        <v>91207</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>768858</v>
+        <v>769400</v>
       </c>
       <c r="R52" t="n">
-        <v>7087093</v>
+        <v>7086922</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6834,12 +6829,12 @@
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>Död, knäckt</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies # Död, knäckt</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6857,7 +6852,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126034872</v>
+        <v>126034869</v>
       </c>
       <c r="B53" t="n">
         <v>91207</v>
@@ -6895,7 +6890,7 @@
         <v>769400</v>
       </c>
       <c r="R53" t="n">
-        <v>7086922</v>
+        <v>7087029</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6951,12 +6946,12 @@
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt</t>
+          <t>granlåga rotvälta</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies # granlåga rotvälta</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6974,32 +6969,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126034869</v>
+        <v>126034877</v>
       </c>
       <c r="B54" t="n">
-        <v>91207</v>
+        <v>91242</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7009,10 +7004,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>769400</v>
+        <v>769560</v>
       </c>
       <c r="R54" t="n">
-        <v>7087029</v>
+        <v>7087013</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7068,12 +7063,12 @@
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>granlåga rotvälta</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga rotvälta</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7091,10 +7086,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126034877</v>
+        <v>126034894</v>
       </c>
       <c r="B55" t="n">
-        <v>91242</v>
+        <v>57653</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7102,34 +7097,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>769560</v>
+        <v>768858</v>
       </c>
       <c r="R55" t="n">
-        <v>7087013</v>
+        <v>7087093</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7185,12 +7185,12 @@
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt</t>
+          <t>Död, knäckt</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies # Död, knäckt</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7208,10 +7208,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126034891</v>
+        <v>126034900</v>
       </c>
       <c r="B56" t="n">
-        <v>57653</v>
+        <v>91238</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7219,39 +7219,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>768972</v>
+        <v>768994</v>
       </c>
       <c r="R56" t="n">
-        <v>7087057</v>
+        <v>7086995</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7307,12 +7302,12 @@
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>Död, stående</t>
+          <t>Gran stående</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies # Död, stående</t>
+          <t>Picea abies # Gran stående</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7330,10 +7325,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126034900</v>
+        <v>126034896</v>
       </c>
       <c r="B57" t="n">
-        <v>91238</v>
+        <v>57653</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7341,34 +7336,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>768994</v>
+        <v>769081</v>
       </c>
       <c r="R57" t="n">
-        <v>7086995</v>
+        <v>7087072</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7403,6 +7403,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Basen av granen</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7422,14 +7427,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL57" t="inlineStr">
-        <is>
-          <t>Gran stående</t>
-        </is>
-      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies # Gran stående</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7447,7 +7447,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126034896</v>
+        <v>126034891</v>
       </c>
       <c r="B58" t="n">
         <v>57653</v>
@@ -7478,7 +7478,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7487,10 +7487,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>769081</v>
+        <v>768972</v>
       </c>
       <c r="R58" t="n">
-        <v>7087072</v>
+        <v>7087057</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7525,11 +7525,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Basen av granen</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7549,9 +7544,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>Död, stående</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7691,10 +7691,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126034888</v>
+        <v>126034903</v>
       </c>
       <c r="B60" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7702,39 +7702,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>768983</v>
+        <v>768982</v>
       </c>
       <c r="R60" t="n">
-        <v>7087104</v>
+        <v>7087094</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7790,12 +7785,12 @@
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Död gran</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Död gran</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7813,32 +7808,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126034903</v>
+        <v>126034870</v>
       </c>
       <c r="B61" t="n">
-        <v>78977</v>
+        <v>91207</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7848,10 +7843,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>768982</v>
+        <v>769323</v>
       </c>
       <c r="R61" t="n">
-        <v>7087094</v>
+        <v>7087087</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7907,12 +7902,12 @@
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>Granlåga över bäck</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies # Död gran</t>
+          <t>Picea abies # Granlåga över bäck</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7930,45 +7925,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126034870</v>
+        <v>126034888</v>
       </c>
       <c r="B62" t="n">
-        <v>91207</v>
+        <v>57653</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>769323</v>
+        <v>768983</v>
       </c>
       <c r="R62" t="n">
-        <v>7087087</v>
+        <v>7087104</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>Granlåga över bäck</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga över bäck</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -4309,48 +4309,57 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125957105</v>
+        <v>125957578</v>
       </c>
       <c r="B32" t="n">
-        <v>91207</v>
+        <v>78977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>769413</v>
+        <v>769345</v>
       </c>
       <c r="R32" t="n">
-        <v>7087074</v>
+        <v>7087087</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4379,7 +4388,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4389,7 +4398,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4436,57 +4445,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125957578</v>
+        <v>125957105</v>
       </c>
       <c r="B33" t="n">
-        <v>78977</v>
+        <v>91207</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>769345</v>
+        <v>769413</v>
       </c>
       <c r="R33" t="n">
-        <v>7087087</v>
+        <v>7087074</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4844,10 +4844,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126034897</v>
+        <v>126034881</v>
       </c>
       <c r="B36" t="n">
-        <v>80080</v>
+        <v>57656</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4855,34 +4855,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>769411</v>
+        <v>768925</v>
       </c>
       <c r="R36" t="n">
-        <v>7086946</v>
+        <v>7087013</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4917,11 +4922,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre tunn sälg, flera bålar av lunglav</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4933,17 +4933,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4961,10 +4966,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126034881</v>
+        <v>126034901</v>
       </c>
       <c r="B37" t="n">
-        <v>57656</v>
+        <v>91260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4972,39 +4977,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>768925</v>
+        <v>768993</v>
       </c>
       <c r="R37" t="n">
-        <v>7087013</v>
+        <v>7087062</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt</t>
+          <t>granlåga knäckt</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
+          <t>Picea abies # granlåga knäckt</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5083,10 +5083,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126034901</v>
+        <v>126034897</v>
       </c>
       <c r="B38" t="n">
-        <v>91260</v>
+        <v>80080</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5094,21 +5094,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>768993</v>
+        <v>769411</v>
       </c>
       <c r="R38" t="n">
-        <v>7087062</v>
+        <v>7086946</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5156,6 +5156,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre tunn sälg, flera bålar av lunglav</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5167,22 +5172,17 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>granlåga knäckt</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga knäckt</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5561,45 +5561,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126034867</v>
+        <v>126034899</v>
       </c>
       <c r="B42" t="n">
-        <v>91207</v>
+        <v>56839</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>avledningsbeteende</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>769351</v>
+        <v>769063</v>
       </c>
       <c r="R42" t="n">
-        <v>7087093</v>
+        <v>7087058</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5642,26 +5651,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>granlåga vindfälle mossbevuxen grov</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies # granlåga vindfälle mossbevuxen grov</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5678,54 +5667,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126034899</v>
+        <v>126034867</v>
       </c>
       <c r="B43" t="n">
-        <v>56839</v>
+        <v>91207</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>avledningsbeteende</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>769063</v>
+        <v>769351</v>
       </c>
       <c r="R43" t="n">
-        <v>7087058</v>
+        <v>7087093</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5768,6 +5748,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>granlåga vindfälle mossbevuxen grov</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies # granlåga vindfälle mossbevuxen grov</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -6735,45 +6735,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126034872</v>
+        <v>126034894</v>
       </c>
       <c r="B52" t="n">
-        <v>91207</v>
+        <v>57653</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>769400</v>
+        <v>768858</v>
       </c>
       <c r="R52" t="n">
-        <v>7086922</v>
+        <v>7087093</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6829,12 +6834,12 @@
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt</t>
+          <t>Död, knäckt</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies # Död, knäckt</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6852,32 +6857,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126034869</v>
+        <v>126034877</v>
       </c>
       <c r="B53" t="n">
-        <v>91207</v>
+        <v>91242</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6887,10 +6892,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>769400</v>
+        <v>769560</v>
       </c>
       <c r="R53" t="n">
-        <v>7087029</v>
+        <v>7087013</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6946,12 +6951,12 @@
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>granlåga rotvälta</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga rotvälta</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6969,32 +6974,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126034877</v>
+        <v>126034872</v>
       </c>
       <c r="B54" t="n">
-        <v>91242</v>
+        <v>91207</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7004,10 +7009,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>769560</v>
+        <v>769400</v>
       </c>
       <c r="R54" t="n">
-        <v>7087013</v>
+        <v>7086922</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7086,50 +7091,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126034894</v>
+        <v>126034869</v>
       </c>
       <c r="B55" t="n">
-        <v>57653</v>
+        <v>91207</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>768858</v>
+        <v>769400</v>
       </c>
       <c r="R55" t="n">
-        <v>7087093</v>
+        <v>7087029</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7185,12 +7185,12 @@
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>Död, knäckt</t>
+          <t>granlåga rotvälta</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies # Död, knäckt</t>
+          <t>Picea abies # granlåga rotvälta</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -8284,7 +8284,7 @@
         <v>126077588</v>
       </c>
       <c r="B65" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>126077587</v>
       </c>
       <c r="B69" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8767,53 +8767,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126077593</v>
+        <v>126077589</v>
       </c>
       <c r="B70" t="n">
-        <v>57602</v>
+        <v>98373</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100067</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>769409</v>
+        <v>769261</v>
       </c>
       <c r="R70" t="n">
-        <v>7086942</v>
+        <v>7086996</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8872,45 +8864,53 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126077589</v>
+        <v>126077593</v>
       </c>
       <c r="B71" t="n">
-        <v>98370</v>
+        <v>57602</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>100067</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>769261</v>
+        <v>769409</v>
       </c>
       <c r="R71" t="n">
-        <v>7086996</v>
+        <v>7086942</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9368,7 +9368,7 @@
         <v>126073254</v>
       </c>
       <c r="B76" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>126073253</v>
       </c>
       <c r="B77" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -4844,10 +4844,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126034881</v>
+        <v>126034897</v>
       </c>
       <c r="B36" t="n">
-        <v>57656</v>
+        <v>80080</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4855,39 +4855,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>768925</v>
+        <v>769411</v>
       </c>
       <c r="R36" t="n">
-        <v>7087013</v>
+        <v>7086946</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4922,6 +4917,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre tunn sälg, flera bålar av lunglav</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4933,22 +4933,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>Granhögstubbe, knäckt</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4966,10 +4961,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126034901</v>
+        <v>126034881</v>
       </c>
       <c r="B37" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4977,34 +4972,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>768993</v>
+        <v>768925</v>
       </c>
       <c r="R37" t="n">
-        <v>7087062</v>
+        <v>7087013</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>granlåga knäckt</t>
+          <t>Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga knäckt</t>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5083,10 +5083,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126034897</v>
+        <v>126034901</v>
       </c>
       <c r="B38" t="n">
-        <v>80080</v>
+        <v>91260</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5094,21 +5094,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>769411</v>
+        <v>768993</v>
       </c>
       <c r="R38" t="n">
-        <v>7086946</v>
+        <v>7087062</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5156,11 +5156,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre tunn sälg, flera bålar av lunglav</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5172,17 +5167,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>granlåga knäckt</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies # granlåga knäckt</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5911,32 +5911,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126034875</v>
+        <v>126034898</v>
       </c>
       <c r="B45" t="n">
-        <v>91242</v>
+        <v>91944</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>769232</v>
+        <v>769524</v>
       </c>
       <c r="R45" t="n">
-        <v>7086940</v>
+        <v>7087083</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5984,6 +5984,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6005,12 +6010,12 @@
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>Granlåga knäckt äldre mossbevuxen</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt äldre mossbevuxen</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6028,32 +6033,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126034898</v>
+        <v>126034875</v>
       </c>
       <c r="B46" t="n">
-        <v>91944</v>
+        <v>91242</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6063,10 +6068,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>769524</v>
+        <v>769232</v>
       </c>
       <c r="R46" t="n">
-        <v>7087083</v>
+        <v>7086940</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6101,11 +6106,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6127,12 +6127,12 @@
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga knäckt äldre mossbevuxen</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlåga knäckt äldre mossbevuxen</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6150,10 +6150,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126034878</v>
+        <v>126034902</v>
       </c>
       <c r="B47" t="n">
-        <v>57656</v>
+        <v>91260</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6161,39 +6161,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>769399</v>
+        <v>769563</v>
       </c>
       <c r="R47" t="n">
-        <v>7086925</v>
+        <v>7087014</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6228,11 +6223,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6241,6 +6231,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies # granlåga knäckt</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6257,10 +6267,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126034902</v>
+        <v>126034878</v>
       </c>
       <c r="B48" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6268,34 +6278,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>769563</v>
+        <v>769399</v>
       </c>
       <c r="R48" t="n">
-        <v>7087014</v>
+        <v>7086925</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6330,6 +6345,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6338,26 +6358,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies # granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -8767,45 +8767,53 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126077589</v>
+        <v>126077593</v>
       </c>
       <c r="B70" t="n">
-        <v>98373</v>
+        <v>57602</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>100067</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>769261</v>
+        <v>769409</v>
       </c>
       <c r="R70" t="n">
-        <v>7086996</v>
+        <v>7086942</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8864,53 +8872,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126077593</v>
+        <v>126077589</v>
       </c>
       <c r="B71" t="n">
-        <v>57602</v>
+        <v>98373</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100067</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>769409</v>
+        <v>769261</v>
       </c>
       <c r="R71" t="n">
-        <v>7086942</v>
+        <v>7086996</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -4178,54 +4178,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125955277</v>
+        <v>125957105</v>
       </c>
       <c r="B31" t="n">
-        <v>78977</v>
+        <v>91207</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>769594</v>
+        <v>769413</v>
       </c>
       <c r="R31" t="n">
-        <v>7087023</v>
+        <v>7087074</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
@@ -4257,7 +4248,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4267,7 +4258,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4278,6 +4269,11 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4309,7 +4305,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125957578</v>
+        <v>125955277</v>
       </c>
       <c r="B32" t="n">
         <v>78977</v>
@@ -4339,7 +4335,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4353,13 +4349,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>769345</v>
+        <v>769594</v>
       </c>
       <c r="R32" t="n">
-        <v>7087087</v>
+        <v>7087023</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4388,7 +4384,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4398,7 +4394,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4409,11 +4405,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4445,48 +4436,57 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125957105</v>
+        <v>125957578</v>
       </c>
       <c r="B33" t="n">
-        <v>91207</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>769413</v>
+        <v>769345</v>
       </c>
       <c r="R33" t="n">
-        <v>7087074</v>
+        <v>7087087</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5561,54 +5561,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126034899</v>
+        <v>126034867</v>
       </c>
       <c r="B42" t="n">
-        <v>56839</v>
+        <v>91207</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>avledningsbeteende</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>769063</v>
+        <v>769351</v>
       </c>
       <c r="R42" t="n">
-        <v>7087058</v>
+        <v>7087093</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5651,6 +5642,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>granlåga vindfälle mossbevuxen grov</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies # granlåga vindfälle mossbevuxen grov</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5667,45 +5678,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126034867</v>
+        <v>126034899</v>
       </c>
       <c r="B43" t="n">
-        <v>91207</v>
+        <v>56839</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>avledningsbeteende</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>769351</v>
+        <v>769063</v>
       </c>
       <c r="R43" t="n">
-        <v>7087093</v>
+        <v>7087058</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5748,26 +5768,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>granlåga vindfälle mossbevuxen grov</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies # granlåga vindfälle mossbevuxen grov</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5911,32 +5911,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126034898</v>
+        <v>126034875</v>
       </c>
       <c r="B45" t="n">
-        <v>91944</v>
+        <v>91242</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>769524</v>
+        <v>769232</v>
       </c>
       <c r="R45" t="n">
-        <v>7087083</v>
+        <v>7086940</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5984,11 +5984,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6010,12 +6005,12 @@
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga knäckt äldre mossbevuxen</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlåga knäckt äldre mossbevuxen</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6033,32 +6028,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126034875</v>
+        <v>126034898</v>
       </c>
       <c r="B46" t="n">
-        <v>91242</v>
+        <v>91944</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6068,10 +6063,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>769232</v>
+        <v>769524</v>
       </c>
       <c r="R46" t="n">
-        <v>7086940</v>
+        <v>7087083</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6106,6 +6101,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6127,12 +6127,12 @@
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>Granlåga knäckt äldre mossbevuxen</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt äldre mossbevuxen</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6735,50 +6735,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126034894</v>
+        <v>126034872</v>
       </c>
       <c r="B52" t="n">
-        <v>57653</v>
+        <v>91207</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>768858</v>
+        <v>769400</v>
       </c>
       <c r="R52" t="n">
-        <v>7087093</v>
+        <v>7086922</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6834,12 +6829,12 @@
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>Död, knäckt</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies # Död, knäckt</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6857,32 +6852,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126034877</v>
+        <v>126034869</v>
       </c>
       <c r="B53" t="n">
-        <v>91242</v>
+        <v>91207</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6892,10 +6887,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>769560</v>
+        <v>769400</v>
       </c>
       <c r="R53" t="n">
-        <v>7087013</v>
+        <v>7087029</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6951,12 +6946,12 @@
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt</t>
+          <t>granlåga rotvälta</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies # granlåga rotvälta</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6974,32 +6969,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126034872</v>
+        <v>126034877</v>
       </c>
       <c r="B54" t="n">
-        <v>91207</v>
+        <v>91242</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7009,10 +7004,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>769400</v>
+        <v>769560</v>
       </c>
       <c r="R54" t="n">
-        <v>7086922</v>
+        <v>7087013</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7091,45 +7086,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126034869</v>
+        <v>126034894</v>
       </c>
       <c r="B55" t="n">
-        <v>91207</v>
+        <v>57653</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>769400</v>
+        <v>768858</v>
       </c>
       <c r="R55" t="n">
-        <v>7087029</v>
+        <v>7087093</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7185,12 +7185,12 @@
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>granlåga rotvälta</t>
+          <t>Död, knäckt</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga rotvälta</t>
+          <t>Picea abies # Död, knäckt</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7208,10 +7208,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126034900</v>
+        <v>126034896</v>
       </c>
       <c r="B56" t="n">
-        <v>91238</v>
+        <v>57653</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7219,34 +7219,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>768994</v>
+        <v>769081</v>
       </c>
       <c r="R56" t="n">
-        <v>7086995</v>
+        <v>7087072</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7281,6 +7286,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Basen av granen</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7300,14 +7310,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL56" t="inlineStr">
-        <is>
-          <t>Gran stående</t>
-        </is>
-      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies # Gran stående</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7325,7 +7330,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126034896</v>
+        <v>126034891</v>
       </c>
       <c r="B57" t="n">
         <v>57653</v>
@@ -7356,7 +7361,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7365,10 +7370,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>769081</v>
+        <v>768972</v>
       </c>
       <c r="R57" t="n">
-        <v>7087072</v>
+        <v>7087057</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7403,11 +7408,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Basen av granen</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7427,9 +7427,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>Död, stående</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7447,10 +7452,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126034891</v>
+        <v>126034900</v>
       </c>
       <c r="B58" t="n">
-        <v>57653</v>
+        <v>91238</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7458,39 +7463,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>768972</v>
+        <v>768994</v>
       </c>
       <c r="R58" t="n">
-        <v>7087057</v>
+        <v>7086995</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>Död, stående</t>
+          <t>Gran stående</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies # Död, stående</t>
+          <t>Picea abies # Gran stående</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -4961,10 +4961,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126034881</v>
+        <v>126034901</v>
       </c>
       <c r="B37" t="n">
-        <v>57656</v>
+        <v>91260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4972,39 +4972,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>768925</v>
+        <v>768993</v>
       </c>
       <c r="R37" t="n">
-        <v>7087013</v>
+        <v>7087062</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5060,12 +5055,12 @@
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>Granhögstubbe, knäckt</t>
+          <t>granlåga knäckt</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
+          <t>Picea abies # granlåga knäckt</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5083,10 +5078,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126034901</v>
+        <v>126034881</v>
       </c>
       <c r="B38" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5094,34 +5089,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>768993</v>
+        <v>768925</v>
       </c>
       <c r="R38" t="n">
-        <v>7087062</v>
+        <v>7087013</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5177,12 +5177,12 @@
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>granlåga knäckt</t>
+          <t>Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga knäckt</t>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -6735,45 +6735,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126034872</v>
+        <v>126034894</v>
       </c>
       <c r="B52" t="n">
-        <v>91207</v>
+        <v>57653</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>769400</v>
+        <v>768858</v>
       </c>
       <c r="R52" t="n">
-        <v>7086922</v>
+        <v>7087093</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6829,12 +6834,12 @@
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt</t>
+          <t>Död, knäckt</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies # Död, knäckt</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6852,7 +6857,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126034869</v>
+        <v>126034872</v>
       </c>
       <c r="B53" t="n">
         <v>91207</v>
@@ -6890,7 +6895,7 @@
         <v>769400</v>
       </c>
       <c r="R53" t="n">
-        <v>7087029</v>
+        <v>7086922</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6946,12 +6951,12 @@
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>granlåga rotvälta</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga rotvälta</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6969,32 +6974,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126034877</v>
+        <v>126034869</v>
       </c>
       <c r="B54" t="n">
-        <v>91242</v>
+        <v>91207</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -7004,10 +7009,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>769560</v>
+        <v>769400</v>
       </c>
       <c r="R54" t="n">
-        <v>7087013</v>
+        <v>7087029</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7063,12 +7068,12 @@
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt</t>
+          <t>granlåga rotvälta</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies # granlåga rotvälta</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7086,10 +7091,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126034894</v>
+        <v>126034877</v>
       </c>
       <c r="B55" t="n">
-        <v>57653</v>
+        <v>91242</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7097,39 +7102,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>768858</v>
+        <v>769560</v>
       </c>
       <c r="R55" t="n">
-        <v>7087093</v>
+        <v>7087013</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7185,12 +7185,12 @@
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>Död, knäckt</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies # Död, knäckt</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -3772,7 +3772,7 @@
         <v>125958446</v>
       </c>
       <c r="B28" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>125956621</v>
       </c>
       <c r="B29" t="n">
-        <v>91238</v>
+        <v>91241</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
         <v>125957531</v>
       </c>
       <c r="B30" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>125957105</v>
       </c>
       <c r="B31" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
         <v>125955277</v>
       </c>
       <c r="B32" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>125957578</v>
       </c>
       <c r="B33" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>125956746</v>
       </c>
       <c r="B34" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>125957354</v>
       </c>
       <c r="B35" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>126034897</v>
       </c>
       <c r="B36" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>126034901</v>
       </c>
       <c r="B37" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>126034881</v>
       </c>
       <c r="B38" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>126034893</v>
       </c>
       <c r="B39" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         <v>126034874</v>
       </c>
       <c r="B40" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>126034892</v>
       </c>
       <c r="B41" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5561,45 +5561,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126034867</v>
+        <v>126034899</v>
       </c>
       <c r="B42" t="n">
-        <v>91207</v>
+        <v>56840</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>avledningsbeteende</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>769351</v>
+        <v>769063</v>
       </c>
       <c r="R42" t="n">
-        <v>7087093</v>
+        <v>7087058</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5642,26 +5651,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>granlåga vindfälle mossbevuxen grov</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies # granlåga vindfälle mossbevuxen grov</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5678,54 +5667,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126034899</v>
+        <v>126034867</v>
       </c>
       <c r="B43" t="n">
-        <v>56839</v>
+        <v>91210</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>avledningsbeteende</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>769063</v>
+        <v>769351</v>
       </c>
       <c r="R43" t="n">
-        <v>7087058</v>
+        <v>7087093</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5768,6 +5748,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>granlåga vindfälle mossbevuxen grov</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies # granlåga vindfälle mossbevuxen grov</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5787,7 +5787,7 @@
         <v>126034889</v>
       </c>
       <c r="B44" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5911,32 +5911,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126034875</v>
+        <v>126034898</v>
       </c>
       <c r="B45" t="n">
-        <v>91242</v>
+        <v>91947</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>769232</v>
+        <v>769524</v>
       </c>
       <c r="R45" t="n">
-        <v>7086940</v>
+        <v>7087083</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5984,6 +5984,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6005,12 +6010,12 @@
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>Granlåga knäckt äldre mossbevuxen</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt äldre mossbevuxen</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6028,32 +6033,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126034898</v>
+        <v>126034875</v>
       </c>
       <c r="B46" t="n">
-        <v>91944</v>
+        <v>91245</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6063,10 +6068,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>769524</v>
+        <v>769232</v>
       </c>
       <c r="R46" t="n">
-        <v>7087083</v>
+        <v>7086940</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6101,11 +6106,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6127,12 +6127,12 @@
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga knäckt äldre mossbevuxen</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlåga knäckt äldre mossbevuxen</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6153,7 +6153,7 @@
         <v>126034902</v>
       </c>
       <c r="B47" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6270,7 +6270,7 @@
         <v>126034878</v>
       </c>
       <c r="B48" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>126034871</v>
       </c>
       <c r="B49" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>126034890</v>
       </c>
       <c r="B50" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>126034880</v>
       </c>
       <c r="B51" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6735,50 +6735,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126034894</v>
+        <v>126034872</v>
       </c>
       <c r="B52" t="n">
-        <v>57653</v>
+        <v>91210</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>768858</v>
+        <v>769400</v>
       </c>
       <c r="R52" t="n">
-        <v>7087093</v>
+        <v>7086922</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6834,12 +6829,12 @@
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>Död, knäckt</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies # Död, knäckt</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6857,10 +6852,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126034872</v>
+        <v>126034869</v>
       </c>
       <c r="B53" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6895,7 +6890,7 @@
         <v>769400</v>
       </c>
       <c r="R53" t="n">
-        <v>7086922</v>
+        <v>7087029</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6951,12 +6946,12 @@
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt</t>
+          <t>granlåga rotvälta</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies # granlåga rotvälta</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6974,45 +6969,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126034869</v>
+        <v>126034894</v>
       </c>
       <c r="B54" t="n">
-        <v>91207</v>
+        <v>57654</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>769400</v>
+        <v>768858</v>
       </c>
       <c r="R54" t="n">
-        <v>7087029</v>
+        <v>7087093</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7068,12 +7068,12 @@
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>granlåga rotvälta</t>
+          <t>Död, knäckt</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga rotvälta</t>
+          <t>Picea abies # Död, knäckt</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7094,7 +7094,7 @@
         <v>126034877</v>
       </c>
       <c r="B55" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>126034896</v>
       </c>
       <c r="B56" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7333,7 +7333,7 @@
         <v>126034891</v>
       </c>
       <c r="B57" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         <v>126034900</v>
       </c>
       <c r="B58" t="n">
-        <v>91238</v>
+        <v>91241</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>126034887</v>
       </c>
       <c r="B59" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7691,10 +7691,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126034903</v>
+        <v>126034888</v>
       </c>
       <c r="B60" t="n">
-        <v>78977</v>
+        <v>57654</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7702,34 +7702,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>768982</v>
+        <v>768983</v>
       </c>
       <c r="R60" t="n">
-        <v>7087094</v>
+        <v>7087104</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7785,12 +7790,12 @@
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies # Död gran</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7808,32 +7813,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126034870</v>
+        <v>126034903</v>
       </c>
       <c r="B61" t="n">
-        <v>91207</v>
+        <v>78980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7843,10 +7848,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>769323</v>
+        <v>768982</v>
       </c>
       <c r="R61" t="n">
-        <v>7087087</v>
+        <v>7087094</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7902,12 +7907,12 @@
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>Granlåga över bäck</t>
+          <t>Död gran</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga över bäck</t>
+          <t>Picea abies # Död gran</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7925,50 +7930,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126034888</v>
+        <v>126034870</v>
       </c>
       <c r="B62" t="n">
-        <v>57653</v>
+        <v>91210</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>768983</v>
+        <v>769323</v>
       </c>
       <c r="R62" t="n">
-        <v>7087104</v>
+        <v>7087087</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Granlåga över bäck</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Granlåga över bäck</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8050,7 +8050,7 @@
         <v>126034873</v>
       </c>
       <c r="B63" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>126034876</v>
       </c>
       <c r="B64" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>126077588</v>
       </c>
       <c r="B65" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>126077586</v>
       </c>
       <c r="B66" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>126077591</v>
       </c>
       <c r="B67" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>126077598</v>
       </c>
       <c r="B68" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>126077587</v>
       </c>
       <c r="B69" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>126077593</v>
       </c>
       <c r="B70" t="n">
-        <v>57602</v>
+        <v>57603</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>126077589</v>
       </c>
       <c r="B71" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>126077590</v>
       </c>
       <c r="B72" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>126077592</v>
       </c>
       <c r="B73" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>126077585</v>
       </c>
       <c r="B74" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9263,7 +9263,7 @@
         <v>126077597</v>
       </c>
       <c r="B75" t="n">
-        <v>58331</v>
+        <v>58334</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>126073254</v>
       </c>
       <c r="B76" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>126073253</v>
       </c>
       <c r="B77" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>126131470</v>
       </c>
       <c r="B78" t="n">
-        <v>91256</v>
+        <v>91259</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>126073252</v>
       </c>
       <c r="B79" t="n">
-        <v>80109</v>
+        <v>80112</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9795,7 +9795,7 @@
         <v>126073251</v>
       </c>
       <c r="B80" t="n">
-        <v>80109</v>
+        <v>80112</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>126073268</v>
       </c>
       <c r="B81" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>126073262</v>
       </c>
       <c r="B82" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>126073257</v>
       </c>
       <c r="B83" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -4178,45 +4178,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125957105</v>
+        <v>125955277</v>
       </c>
       <c r="B31" t="n">
-        <v>91210</v>
+        <v>78980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>769413</v>
+        <v>769594</v>
       </c>
       <c r="R31" t="n">
-        <v>7087074</v>
+        <v>7087023</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
@@ -4248,7 +4257,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4258,7 +4267,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4269,11 +4278,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4305,7 +4309,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125955277</v>
+        <v>125957578</v>
       </c>
       <c r="B32" t="n">
         <v>78980</v>
@@ -4335,7 +4339,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4349,13 +4353,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>769594</v>
+        <v>769345</v>
       </c>
       <c r="R32" t="n">
-        <v>7087023</v>
+        <v>7087087</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4384,7 +4388,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4394,7 +4398,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4405,6 +4409,11 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4436,57 +4445,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125957578</v>
+        <v>125957105</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>91210</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>769345</v>
+        <v>769413</v>
       </c>
       <c r="R33" t="n">
-        <v>7087087</v>
+        <v>7087074</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4844,10 +4844,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126034897</v>
+        <v>126034901</v>
       </c>
       <c r="B36" t="n">
-        <v>80083</v>
+        <v>91263</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4855,21 +4855,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>769411</v>
+        <v>768993</v>
       </c>
       <c r="R36" t="n">
-        <v>7086946</v>
+        <v>7087062</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4917,11 +4917,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre tunn sälg, flera bålar av lunglav</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4933,17 +4928,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>granlåga knäckt</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies # granlåga knäckt</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126034901</v>
+        <v>126034897</v>
       </c>
       <c r="B37" t="n">
-        <v>91263</v>
+        <v>80083</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4972,21 +4972,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4996,10 +4996,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>768993</v>
+        <v>769411</v>
       </c>
       <c r="R37" t="n">
-        <v>7087062</v>
+        <v>7086946</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5034,6 +5034,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre tunn sälg, flera bålar av lunglav</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5045,22 +5050,17 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>granlåga knäckt</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga knäckt</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5561,54 +5561,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126034899</v>
+        <v>126034867</v>
       </c>
       <c r="B42" t="n">
-        <v>56840</v>
+        <v>91210</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>avledningsbeteende</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>769063</v>
+        <v>769351</v>
       </c>
       <c r="R42" t="n">
-        <v>7087058</v>
+        <v>7087093</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5651,6 +5642,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>granlåga vindfälle mossbevuxen grov</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies # granlåga vindfälle mossbevuxen grov</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5667,45 +5678,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126034867</v>
+        <v>126034899</v>
       </c>
       <c r="B43" t="n">
-        <v>91210</v>
+        <v>56840</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>avledningsbeteende</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>769351</v>
+        <v>769063</v>
       </c>
       <c r="R43" t="n">
-        <v>7087093</v>
+        <v>7087058</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5748,26 +5768,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>granlåga vindfälle mossbevuxen grov</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies # granlåga vindfälle mossbevuxen grov</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -4178,54 +4178,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125955277</v>
+        <v>125957105</v>
       </c>
       <c r="B31" t="n">
-        <v>78980</v>
+        <v>91210</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>769594</v>
+        <v>769413</v>
       </c>
       <c r="R31" t="n">
-        <v>7087023</v>
+        <v>7087074</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
@@ -4257,7 +4248,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4267,7 +4258,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4278,6 +4269,11 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4309,7 +4305,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125957578</v>
+        <v>125955277</v>
       </c>
       <c r="B32" t="n">
         <v>78980</v>
@@ -4339,7 +4335,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4353,13 +4349,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>769345</v>
+        <v>769594</v>
       </c>
       <c r="R32" t="n">
-        <v>7087087</v>
+        <v>7087023</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4388,7 +4384,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4398,7 +4394,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4409,11 +4405,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4445,48 +4436,57 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125957105</v>
+        <v>125957578</v>
       </c>
       <c r="B33" t="n">
-        <v>91210</v>
+        <v>78980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>769413</v>
+        <v>769345</v>
       </c>
       <c r="R33" t="n">
-        <v>7087074</v>
+        <v>7087087</v>
       </c>
       <c r="S33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4844,10 +4844,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126034901</v>
+        <v>126034897</v>
       </c>
       <c r="B36" t="n">
-        <v>91263</v>
+        <v>80083</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4855,21 +4855,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4879,10 +4879,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>768993</v>
+        <v>769411</v>
       </c>
       <c r="R36" t="n">
-        <v>7087062</v>
+        <v>7086946</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4917,6 +4917,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre tunn sälg, flera bålar av lunglav</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4928,22 +4933,17 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>granlåga knäckt</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga knäckt</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4961,10 +4961,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126034897</v>
+        <v>126034901</v>
       </c>
       <c r="B37" t="n">
-        <v>80083</v>
+        <v>91263</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4972,21 +4972,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4996,10 +4996,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>769411</v>
+        <v>768993</v>
       </c>
       <c r="R37" t="n">
-        <v>7086946</v>
+        <v>7087062</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5034,11 +5034,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre tunn sälg, flera bålar av lunglav</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5050,17 +5045,22 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>granlåga knäckt</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies # granlåga knäckt</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5200,50 +5200,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126034893</v>
+        <v>126034874</v>
       </c>
       <c r="B39" t="n">
-        <v>57654</v>
+        <v>91210</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>768983</v>
+        <v>769382</v>
       </c>
       <c r="R39" t="n">
-        <v>7087095</v>
+        <v>7087083</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5299,12 +5294,12 @@
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>Död, stående</t>
+          <t>Granlåga delvis utan bark</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies # Död, stående</t>
+          <t>Picea abies # Granlåga delvis utan bark</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5322,45 +5317,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126034874</v>
+        <v>126034893</v>
       </c>
       <c r="B40" t="n">
-        <v>91210</v>
+        <v>57654</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>769382</v>
+        <v>768983</v>
       </c>
       <c r="R40" t="n">
-        <v>7087083</v>
+        <v>7087095</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>Granlåga delvis utan bark</t>
+          <t>Död, stående</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga delvis utan bark</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5561,45 +5561,54 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126034867</v>
+        <v>126034899</v>
       </c>
       <c r="B42" t="n">
-        <v>91210</v>
+        <v>56840</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>avledningsbeteende</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>769351</v>
+        <v>769063</v>
       </c>
       <c r="R42" t="n">
-        <v>7087093</v>
+        <v>7087058</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5642,26 +5651,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>granlåga vindfälle mossbevuxen grov</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies # granlåga vindfälle mossbevuxen grov</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5678,54 +5667,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126034899</v>
+        <v>126034867</v>
       </c>
       <c r="B43" t="n">
-        <v>56840</v>
+        <v>91210</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>avledningsbeteende</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>769063</v>
+        <v>769351</v>
       </c>
       <c r="R43" t="n">
-        <v>7087058</v>
+        <v>7087093</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5768,6 +5748,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>granlåga vindfälle mossbevuxen grov</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies # granlåga vindfälle mossbevuxen grov</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -6735,32 +6735,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126034872</v>
+        <v>126034877</v>
       </c>
       <c r="B52" t="n">
-        <v>91210</v>
+        <v>91245</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6770,10 +6770,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>769400</v>
+        <v>769560</v>
       </c>
       <c r="R52" t="n">
-        <v>7086922</v>
+        <v>7087013</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6852,7 +6852,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126034869</v>
+        <v>126034872</v>
       </c>
       <c r="B53" t="n">
         <v>91210</v>
@@ -6890,7 +6890,7 @@
         <v>769400</v>
       </c>
       <c r="R53" t="n">
-        <v>7087029</v>
+        <v>7086922</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6946,12 +6946,12 @@
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>granlåga rotvälta</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga rotvälta</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6969,50 +6969,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126034894</v>
+        <v>126034869</v>
       </c>
       <c r="B54" t="n">
-        <v>57654</v>
+        <v>91210</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>768858</v>
+        <v>769400</v>
       </c>
       <c r="R54" t="n">
-        <v>7087093</v>
+        <v>7087029</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7068,12 +7063,12 @@
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>Död, knäckt</t>
+          <t>granlåga rotvälta</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies # Död, knäckt</t>
+          <t>Picea abies # granlåga rotvälta</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7091,10 +7086,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126034877</v>
+        <v>126034894</v>
       </c>
       <c r="B55" t="n">
-        <v>91245</v>
+        <v>57654</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7102,34 +7097,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>769560</v>
+        <v>768858</v>
       </c>
       <c r="R55" t="n">
-        <v>7087013</v>
+        <v>7087093</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7185,12 +7185,12 @@
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt</t>
+          <t>Död, knäckt</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies # Död, knäckt</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7208,7 +7208,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126034896</v>
+        <v>126034891</v>
       </c>
       <c r="B56" t="n">
         <v>57654</v>
@@ -7239,7 +7239,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7248,10 +7248,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>769081</v>
+        <v>768972</v>
       </c>
       <c r="R56" t="n">
-        <v>7087072</v>
+        <v>7087057</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7286,11 +7286,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Basen av granen</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7310,9 +7305,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>Död, stående</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7330,7 +7330,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126034891</v>
+        <v>126034896</v>
       </c>
       <c r="B57" t="n">
         <v>57654</v>
@@ -7361,7 +7361,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7370,10 +7370,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>768972</v>
+        <v>769081</v>
       </c>
       <c r="R57" t="n">
-        <v>7087057</v>
+        <v>7087072</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7408,6 +7408,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Basen av granen</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7427,14 +7432,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL57" t="inlineStr">
-        <is>
-          <t>Död, stående</t>
-        </is>
-      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies # Död, stående</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7691,10 +7691,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126034888</v>
+        <v>126034903</v>
       </c>
       <c r="B60" t="n">
-        <v>57654</v>
+        <v>78980</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7702,39 +7702,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>768983</v>
+        <v>768982</v>
       </c>
       <c r="R60" t="n">
-        <v>7087104</v>
+        <v>7087094</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7790,12 +7785,12 @@
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Död gran</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Död gran</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7813,32 +7808,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126034903</v>
+        <v>126034870</v>
       </c>
       <c r="B61" t="n">
-        <v>78980</v>
+        <v>91210</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7848,10 +7843,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>768982</v>
+        <v>769323</v>
       </c>
       <c r="R61" t="n">
-        <v>7087094</v>
+        <v>7087087</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7907,12 +7902,12 @@
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>Granlåga över bäck</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies # Död gran</t>
+          <t>Picea abies # Granlåga över bäck</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7930,45 +7925,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126034870</v>
+        <v>126034888</v>
       </c>
       <c r="B62" t="n">
-        <v>91210</v>
+        <v>57654</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>769323</v>
+        <v>768983</v>
       </c>
       <c r="R62" t="n">
-        <v>7087087</v>
+        <v>7087104</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>Granlåga över bäck</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga över bäck</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8047,32 +8047,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126034873</v>
+        <v>126034876</v>
       </c>
       <c r="B63" t="n">
-        <v>91210</v>
+        <v>91245</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8082,10 +8082,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>768910</v>
+        <v>769088</v>
       </c>
       <c r="R63" t="n">
-        <v>7087060</v>
+        <v>7087046</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -8141,12 +8141,12 @@
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt</t>
+          <t>Granlåga, knäckt, delvis nedsjunken i mossa</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies # Granlåga, knäckt, delvis nedsjunken i mossa</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8164,32 +8164,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126034876</v>
+        <v>126034873</v>
       </c>
       <c r="B64" t="n">
-        <v>91245</v>
+        <v>91210</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8199,10 +8199,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>769088</v>
+        <v>768910</v>
       </c>
       <c r="R64" t="n">
-        <v>7087046</v>
+        <v>7087060</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8258,12 +8258,12 @@
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>Granlåga, knäckt, delvis nedsjunken i mossa</t>
+          <t>Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt, delvis nedsjunken i mossa</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -5911,32 +5911,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126034898</v>
+        <v>126034875</v>
       </c>
       <c r="B45" t="n">
-        <v>91947</v>
+        <v>91245</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>769524</v>
+        <v>769232</v>
       </c>
       <c r="R45" t="n">
-        <v>7087083</v>
+        <v>7086940</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5984,11 +5984,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6010,12 +6005,12 @@
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>Granlåga</t>
+          <t>Granlåga knäckt äldre mossbevuxen</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies # Granlåga knäckt äldre mossbevuxen</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6033,32 +6028,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126034875</v>
+        <v>126034898</v>
       </c>
       <c r="B46" t="n">
-        <v>91245</v>
+        <v>91947</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6068,10 +6063,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>769232</v>
+        <v>769524</v>
       </c>
       <c r="R46" t="n">
-        <v>7086940</v>
+        <v>7087083</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6106,6 +6101,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6127,12 +6127,12 @@
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>Granlåga knäckt äldre mossbevuxen</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga knäckt äldre mossbevuxen</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6150,10 +6150,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126034902</v>
+        <v>126034878</v>
       </c>
       <c r="B47" t="n">
-        <v>91263</v>
+        <v>57657</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6161,34 +6161,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>769563</v>
+        <v>769399</v>
       </c>
       <c r="R47" t="n">
-        <v>7087014</v>
+        <v>7086925</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6223,6 +6228,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6231,26 +6241,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies # granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6267,10 +6257,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126034878</v>
+        <v>126034902</v>
       </c>
       <c r="B48" t="n">
-        <v>57657</v>
+        <v>91263</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6278,39 +6268,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>769399</v>
+        <v>769563</v>
       </c>
       <c r="R48" t="n">
-        <v>7086925</v>
+        <v>7087014</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6345,11 +6330,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6358,6 +6338,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies # granlåga knäckt</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -6150,10 +6150,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126034878</v>
+        <v>126034902</v>
       </c>
       <c r="B47" t="n">
-        <v>57657</v>
+        <v>91263</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6161,39 +6161,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>769399</v>
+        <v>769563</v>
       </c>
       <c r="R47" t="n">
-        <v>7086925</v>
+        <v>7087014</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6228,11 +6223,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6241,6 +6231,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>granlåga knäckt</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies # granlåga knäckt</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6257,10 +6267,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126034902</v>
+        <v>126034878</v>
       </c>
       <c r="B48" t="n">
-        <v>91263</v>
+        <v>57657</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6268,34 +6278,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>769563</v>
+        <v>769399</v>
       </c>
       <c r="R48" t="n">
-        <v>7087014</v>
+        <v>7086925</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6330,6 +6345,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6338,26 +6358,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies # granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -7208,10 +7208,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126034891</v>
+        <v>126034900</v>
       </c>
       <c r="B56" t="n">
-        <v>57654</v>
+        <v>91241</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7219,39 +7219,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>768972</v>
+        <v>768994</v>
       </c>
       <c r="R56" t="n">
-        <v>7087057</v>
+        <v>7086995</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7307,12 +7302,12 @@
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>Död, stående</t>
+          <t>Gran stående</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies # Död, stående</t>
+          <t>Picea abies # Gran stående</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7330,7 +7325,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126034896</v>
+        <v>126034891</v>
       </c>
       <c r="B57" t="n">
         <v>57654</v>
@@ -7361,7 +7356,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7370,10 +7365,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>769081</v>
+        <v>768972</v>
       </c>
       <c r="R57" t="n">
-        <v>7087072</v>
+        <v>7087057</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7408,11 +7403,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Basen av granen</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7432,9 +7422,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>Död, stående</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7452,10 +7447,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126034900</v>
+        <v>126034896</v>
       </c>
       <c r="B58" t="n">
-        <v>91241</v>
+        <v>57654</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7463,34 +7458,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>768994</v>
+        <v>769081</v>
       </c>
       <c r="R58" t="n">
-        <v>7086995</v>
+        <v>7087072</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7525,6 +7525,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Basen av granen</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7544,14 +7549,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL58" t="inlineStr">
-        <is>
-          <t>Gran stående</t>
-        </is>
-      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies # Gran stående</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY83"/>
+  <dimension ref="A1:AY84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10235,6 +10235,141 @@
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>125593294</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Mossamyran, Mossamyran, Vb</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>769751</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7086871</v>
+      </c>
+      <c r="S84" t="n">
+        <v>2</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Katharina Radloff</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -10240,7 +10240,7 @@
         <v>125593294</v>
       </c>
       <c r="B84" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -10240,7 +10240,7 @@
         <v>125593294</v>
       </c>
       <c r="B84" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AY81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95744068</v>
+        <v>126034898</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>S om Mossaberget, Vb</t>
+          <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>768838.2186220367</v>
+        <v>769524</v>
       </c>
       <c r="R2" t="n">
-        <v>7087000.232991162</v>
+        <v>7087083</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,100 +740,114 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-08-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-08-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Kollekt</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111316855</v>
+        <v>125956621</v>
       </c>
       <c r="B3" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mossaberget SV Täfteå, Vb</t>
+          <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768836.2269898241</v>
+        <v>769594</v>
       </c>
       <c r="R3" t="n">
-        <v>7086987.190273426</v>
+        <v>7087023</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +871,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,35 +898,45 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>död gran</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111316854</v>
+        <v>126034900</v>
       </c>
       <c r="B4" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,37 +944,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mossaberget SV Täfteå, Vb</t>
+          <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768836.2269898241</v>
+        <v>768994</v>
       </c>
       <c r="R4" t="n">
-        <v>7086987.190273426</v>
+        <v>7086995</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +998,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,35 +1015,45 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Gran stående</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>död gran</t>
+          <t>Picea abies # Gran stående</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Garpebring, Åsa Gustafsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111740915</v>
+        <v>111740892</v>
       </c>
       <c r="B5" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,39 +1061,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sandån-Täftefjärden, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>769966</v>
+        <v>769962</v>
       </c>
       <c r="R5" t="n">
-        <v>7087033</v>
+        <v>7087025</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1133,53 +1147,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111740881</v>
+        <v>126034875</v>
       </c>
       <c r="B6" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sandån-Täftefjärden, Vb</t>
+          <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>769995</v>
+        <v>769232</v>
       </c>
       <c r="R6" t="n">
-        <v>7086931</v>
+        <v>7086940</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,12 +1212,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,31 +1228,46 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Granlåga knäckt äldre mossbevuxen</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga knäckt äldre mossbevuxen</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111740957</v>
+        <v>126034876</v>
       </c>
       <c r="B7" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,37 +1275,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sandån-Täftefjärden, Vb</t>
+          <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>769801</v>
+        <v>769088</v>
       </c>
       <c r="R7" t="n">
-        <v>7086946</v>
+        <v>7087046</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,12 +1329,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,31 +1345,46 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>Granlåga, knäckt, delvis nedsjunken i mossa</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga, knäckt, delvis nedsjunken i mossa</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111740892</v>
+        <v>126034877</v>
       </c>
       <c r="B8" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,17 +1412,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sandån-Täftefjärden, Vb</t>
+          <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>769961</v>
+        <v>769560</v>
       </c>
       <c r="R8" t="n">
-        <v>7087025</v>
+        <v>7087013</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,12 +1446,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,66 +1462,81 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>Granlåga, knäckt</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga, knäckt</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111740882</v>
+        <v>126077586</v>
       </c>
       <c r="B9" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sandån-Täftefjärden, Vb</t>
+          <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>769926</v>
+        <v>769682</v>
       </c>
       <c r="R9" t="n">
-        <v>7086947</v>
+        <v>7087017</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,12 +1563,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1529,65 +1583,69 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111740883</v>
+        <v>126131470</v>
       </c>
       <c r="B10" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sandån-Täftefjärden, Vb</t>
+          <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>768902</v>
+        <v>769374</v>
       </c>
       <c r="R10" t="n">
-        <v>7087045</v>
+        <v>7086933</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1611,12 +1669,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2025-06-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1627,66 +1695,81 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111740916</v>
+        <v>111316850</v>
       </c>
       <c r="B11" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sandån-Täftefjärden, Vb</t>
+          <t>Mossaberget SV Täfteå, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>768945</v>
+        <v>768829</v>
       </c>
       <c r="R11" t="n">
-        <v>7086997</v>
+        <v>7087029</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,12 +1796,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1727,50 +1810,56 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>grenar på gammal asp</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111740936</v>
+        <v>111740881</v>
       </c>
       <c r="B12" t="n">
-        <v>89790</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6040186</v>
+        <v>5447</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1869,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>769779</v>
+        <v>769995</v>
       </c>
       <c r="R12" t="n">
-        <v>7087057</v>
+        <v>7086931</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,15 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111740938</v>
+        <v>111740882</v>
       </c>
       <c r="B13" t="n">
-        <v>73634</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,21 +1942,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1966,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>768917</v>
+        <v>769927</v>
       </c>
       <c r="R13" t="n">
-        <v>7087064</v>
+        <v>7086947</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,37 +2028,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111740956</v>
+        <v>111740883</v>
       </c>
       <c r="B14" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>769810</v>
+        <v>768902</v>
       </c>
       <c r="R14" t="n">
-        <v>7086964</v>
+        <v>7087045</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,53 +2125,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111740961</v>
+        <v>125957105</v>
       </c>
       <c r="B15" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sandån-Täftefjärden, Vb</t>
+          <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>769989</v>
+        <v>769413</v>
       </c>
       <c r="R15" t="n">
-        <v>7086946</v>
+        <v>7087074</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2116,12 +2190,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2132,69 +2216,84 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125595361</v>
+        <v>126034867</v>
       </c>
       <c r="B16" t="n">
-        <v>57649</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Baggöbäcken, Baggöbäcken, Vb</t>
+          <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>770056</v>
+        <v>769351</v>
       </c>
       <c r="R16" t="n">
-        <v>7086839</v>
+        <v>7087093</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2218,22 +2317,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:14</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2245,11 +2334,6 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AJ16" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2260,73 +2344,73 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>granlåga vindfälle mossbevuxen grov</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # granlåga vindfälle mossbevuxen grov</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125598713</v>
+        <v>126034869</v>
       </c>
       <c r="B17" t="n">
-        <v>57649</v>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
+          <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>770013</v>
+        <v>769400</v>
       </c>
       <c r="R17" t="n">
-        <v>7086998</v>
+        <v>7087029</v>
       </c>
       <c r="S17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2350,22 +2434,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,11 +2451,6 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AJ17" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2392,77 +2461,73 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>granlåga rotvälta</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # granlåga rotvälta</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125592468</v>
+        <v>126034870</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mossamyran, Mossamyran, Vb</t>
+          <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>769672</v>
+        <v>769323</v>
       </c>
       <c r="R18" t="n">
-        <v>7086895</v>
+        <v>7087087</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2486,22 +2551,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:45</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:45</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2513,11 +2568,6 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2528,73 +2578,73 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>Granlåga över bäck</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga över bäck</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125595152</v>
+        <v>126034871</v>
       </c>
       <c r="B19" t="n">
-        <v>57649</v>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Baggöbäcken, Baggöbäcken, Vb</t>
+          <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>770034</v>
+        <v>768896</v>
       </c>
       <c r="R19" t="n">
-        <v>7086842</v>
+        <v>7087072</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2618,22 +2668,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:09</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:09</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2645,11 +2685,6 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AJ19" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2660,77 +2695,73 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Granlåga, knäckt,  tunnare nedsänkt mossa</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga, knäckt,  tunnare nedsänkt mossa</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125601124</v>
+        <v>126034872</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mossamyran, Mossamyran, Vb</t>
+          <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>769765</v>
+        <v>769400</v>
       </c>
       <c r="R20" t="n">
-        <v>7087093</v>
+        <v>7086922</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2754,22 +2785,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2781,11 +2802,6 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2796,73 +2812,73 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Granlåga, knäckt</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125598946</v>
+        <v>126034873</v>
       </c>
       <c r="B21" t="n">
-        <v>57649</v>
+        <v>91872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
+          <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>769979</v>
+        <v>768910</v>
       </c>
       <c r="R21" t="n">
-        <v>7087051</v>
+        <v>7087060</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2886,22 +2902,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2913,11 +2919,6 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AJ21" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2928,79 +2929,73 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Granlåga, knäckt</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga, knäckt</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125596546</v>
+        <v>126034874</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Baggöbäcken, Baggöbäcken, Vb</t>
+          <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>770046</v>
+        <v>769382</v>
       </c>
       <c r="R22" t="n">
-        <v>7086894</v>
+        <v>7087083</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3024,22 +3019,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:48</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:48</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3048,15 +3033,9 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AJ22" t="inlineStr">
         <is>
           <t>gran</t>
@@ -3067,77 +3046,73 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Granlåga delvis utan bark</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Granlåga delvis utan bark</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125592263</v>
+        <v>126077585</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mossamyran, Mossamyran, Vb</t>
+          <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>769646</v>
+        <v>769715</v>
       </c>
       <c r="R23" t="n">
-        <v>7086880</v>
+        <v>7087020</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3161,22 +3136,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:39</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:39</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3187,50 +3152,30 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125599815</v>
+        <v>95744068</v>
       </c>
       <c r="B24" t="n">
-        <v>78973</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3251,29 +3196,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sandån, Sandån, Vb</t>
+          <t>S om Mossaberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>770018</v>
+        <v>768838</v>
       </c>
       <c r="R24" t="n">
-        <v>7087094</v>
+        <v>7087000</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3297,22 +3233,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2021-08-24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2021-08-24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3323,89 +3249,64 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125599155</v>
+        <v>111316854</v>
       </c>
       <c r="B25" t="n">
-        <v>57649</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
+          <t>Mossaberget SV Täfteå, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>769958</v>
+        <v>768836</v>
       </c>
       <c r="R25" t="n">
-        <v>7087078</v>
+        <v>7086987</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3429,22 +3330,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3456,88 +3347,68 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>död gran</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125598057</v>
+        <v>111740961</v>
       </c>
       <c r="B26" t="n">
-        <v>57649</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
+          <t>Sandån-Täftefjärden, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>770047</v>
+        <v>769988</v>
       </c>
       <c r="R26" t="n">
-        <v>7086919</v>
+        <v>7086947</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3561,22 +3432,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:34</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3587,63 +3448,48 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125597783</v>
+        <v>125592263</v>
       </c>
       <c r="B27" t="n">
-        <v>57656</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3651,36 +3497,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
+          <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>770048</v>
+        <v>769646</v>
       </c>
       <c r="R27" t="n">
-        <v>7086917</v>
+        <v>7086880</v>
       </c>
       <c r="S27" t="n">
         <v>2</v>
@@ -3712,7 +3543,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3722,7 +3553,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3769,47 +3600,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125958446</v>
+        <v>125592468</v>
       </c>
       <c r="B28" t="n">
-        <v>58027</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3818,13 +3644,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>769311</v>
+        <v>769672</v>
       </c>
       <c r="R28" t="n">
-        <v>7087040</v>
+        <v>7086895</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3848,22 +3674,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3877,22 +3703,22 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Blåbärsblandskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3910,57 +3736,59 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125956621</v>
+        <v>125596546</v>
       </c>
       <c r="B29" t="n">
-        <v>91241</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mossamyran, Mossamyran, Vb</t>
+          <t>Baggöbäcken, Baggöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>769594</v>
+        <v>770046</v>
       </c>
       <c r="R29" t="n">
-        <v>7087023</v>
+        <v>7086894</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3984,22 +3812,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4008,6 +3836,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4046,53 +3875,57 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125957531</v>
+        <v>125599815</v>
       </c>
       <c r="B30" t="n">
-        <v>57654</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mossamyran, Mossamyran, Vb</t>
+          <t>Sandån, Sandån, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>769372</v>
+        <v>770018</v>
       </c>
       <c r="R30" t="n">
-        <v>7087093</v>
+        <v>7087094</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4116,22 +3949,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4178,45 +4011,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125957105</v>
+        <v>125601124</v>
       </c>
       <c r="B31" t="n">
-        <v>91210</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>769413</v>
+        <v>769765</v>
       </c>
       <c r="R31" t="n">
-        <v>7087074</v>
+        <v>7087093</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
@@ -4243,22 +4085,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4308,11 +4150,11 @@
         <v>125955277</v>
       </c>
       <c r="B32" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -4436,14 +4278,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125957578</v>
+        <v>125956746</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4466,12 +4308,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4480,10 +4322,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>769345</v>
+        <v>769483</v>
       </c>
       <c r="R33" t="n">
-        <v>7087087</v>
+        <v>7087082</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -4515,7 +4357,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4525,7 +4367,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4572,14 +4414,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125956746</v>
+        <v>125957354</v>
       </c>
       <c r="B34" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4602,12 +4444,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4616,13 +4458,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>769483</v>
+        <v>769389</v>
       </c>
       <c r="R34" t="n">
-        <v>7087082</v>
+        <v>7087055</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4651,7 +4493,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4661,7 +4503,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4708,14 +4550,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125957354</v>
+        <v>125957578</v>
       </c>
       <c r="B35" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4738,7 +4580,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4752,13 +4594,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>769389</v>
+        <v>769345</v>
       </c>
       <c r="R35" t="n">
-        <v>7087055</v>
+        <v>7087087</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4787,7 +4629,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4797,7 +4639,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4844,32 +4686,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126034897</v>
+        <v>126034903</v>
       </c>
       <c r="B36" t="n">
-        <v>80083</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4879,10 +4721,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>769411</v>
+        <v>768982</v>
       </c>
       <c r="R36" t="n">
-        <v>7086946</v>
+        <v>7087094</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4917,11 +4759,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre tunn sälg, flera bålar av lunglav</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4933,17 +4770,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>Död gran</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies # Död gran</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4961,48 +4803,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126034901</v>
+        <v>126073262</v>
       </c>
       <c r="B37" t="n">
-        <v>91263</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mossamyran, Vb</t>
+          <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>768993</v>
+        <v>769557</v>
       </c>
       <c r="R37" t="n">
-        <v>7087062</v>
+        <v>7086952</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5026,12 +4868,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5042,46 +4884,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>granlåga knäckt</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Picea abies # granlåga knäckt</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126034881</v>
+        <v>111740938</v>
       </c>
       <c r="B38" t="n">
-        <v>57657</v>
+        <v>75428</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5089,42 +4911,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6426</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mossamyran, Vb</t>
+          <t>Sandån-Täftefjärden, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>768925</v>
+        <v>768917</v>
       </c>
       <c r="R38" t="n">
-        <v>7087013</v>
+        <v>7087064</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5148,12 +4965,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5164,68 +4981,48 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>Granhögstubbe, knäckt</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Picea abies # Granhögstubbe, knäckt</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126034874</v>
+        <v>126034897</v>
       </c>
       <c r="B39" t="n">
-        <v>91210</v>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5235,10 +5032,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>769382</v>
+        <v>769411</v>
       </c>
       <c r="R39" t="n">
-        <v>7087083</v>
+        <v>7086946</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5273,6 +5070,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre tunn sälg, flera bålar av lunglav</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5284,22 +5086,17 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>Granlåga delvis utan bark</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga delvis utan bark</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5317,10 +5114,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126034893</v>
+        <v>126073257</v>
       </c>
       <c r="B40" t="n">
-        <v>57654</v>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5328,42 +5125,40 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mossamyran, Vb</t>
+          <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>768983</v>
+        <v>769727</v>
       </c>
       <c r="R40" t="n">
-        <v>7087095</v>
+        <v>7086890</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5387,12 +5182,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5401,91 +5196,85 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>Död, stående</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies # Död, stående</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126034892</v>
+        <v>126073251</v>
       </c>
       <c r="B41" t="n">
-        <v>57654</v>
+        <v>80461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mossamyran, Vb</t>
+          <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>768979</v>
+        <v>769759</v>
       </c>
       <c r="R41" t="n">
-        <v>7087095</v>
+        <v>7086899</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5509,12 +5298,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5523,48 +5312,44 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>Död, stående</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies # Död, stående</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126034867</v>
+        <v>126073252</v>
       </c>
       <c r="B42" t="n">
-        <v>91210</v>
+        <v>80461</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5572,37 +5357,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mossamyran, Vb</t>
+          <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>769351</v>
+        <v>769723</v>
       </c>
       <c r="R42" t="n">
-        <v>7087093</v>
+        <v>7086893</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5626,12 +5411,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5642,93 +5427,67 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>granlåga vindfälle mossbevuxen grov</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies # granlåga vindfälle mossbevuxen grov</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126034899</v>
+        <v>126073268</v>
       </c>
       <c r="B43" t="n">
-        <v>56840</v>
+        <v>80467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>avledningsbeteende</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mossamyran, Vb</t>
+          <t>Ultervik, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>769063</v>
+        <v>769724</v>
       </c>
       <c r="R43" t="n">
-        <v>7087058</v>
+        <v>7086894</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5752,12 +5511,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5766,32 +5525,48 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Maria Wikdahl</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126034889</v>
+        <v>111740915</v>
       </c>
       <c r="B44" t="n">
-        <v>57654</v>
+        <v>57950</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5815,22 +5590,22 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mossamyran, Vb</t>
+          <t>Sandån-Täftefjärden, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>768845</v>
+        <v>769966</v>
       </c>
       <c r="R44" t="n">
-        <v>7087079</v>
+        <v>7087033</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5854,17 +5629,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Aktiva trämyror</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5875,84 +5645,64 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL44" t="inlineStr">
-        <is>
-          <t>Död, stående</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies # Död, stående</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126034875</v>
+        <v>111740916</v>
       </c>
       <c r="B45" t="n">
-        <v>91245</v>
+        <v>57950</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mossamyran, Vb</t>
+          <t>Sandån-Täftefjärden, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>769232</v>
+        <v>768945</v>
       </c>
       <c r="R45" t="n">
-        <v>7086940</v>
+        <v>7086997</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5976,12 +5726,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5992,84 +5742,72 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL45" t="inlineStr">
-        <is>
-          <t>Granlåga knäckt äldre mossbevuxen</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga knäckt äldre mossbevuxen</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126034898</v>
+        <v>125593294</v>
       </c>
       <c r="B46" t="n">
-        <v>91947</v>
+        <v>57972</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>67</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mossamyran, Vb</t>
+          <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>769524</v>
+        <v>769751</v>
       </c>
       <c r="R46" t="n">
-        <v>7087083</v>
+        <v>7086871</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6093,17 +5831,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Kollekt</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6115,6 +5858,11 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
       <c r="AJ46" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6125,52 +5873,47 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126034878</v>
+        <v>125595152</v>
       </c>
       <c r="B47" t="n">
-        <v>57657</v>
+        <v>57950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6186,17 +5929,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mossamyran, Vb</t>
+          <t>Baggöbäcken, Baggöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>769399</v>
+        <v>770034</v>
       </c>
       <c r="R47" t="n">
-        <v>7086925</v>
+        <v>7086842</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6220,17 +5963,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6241,64 +5989,89 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126034902</v>
+        <v>125595361</v>
       </c>
       <c r="B48" t="n">
-        <v>91263</v>
+        <v>57950</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mossamyran, Vb</t>
+          <t>Baggöbäcken, Baggöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>769563</v>
+        <v>770056</v>
       </c>
       <c r="R48" t="n">
-        <v>7087014</v>
+        <v>7086839</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6322,12 +6095,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6339,6 +6122,11 @@
       <c r="AG48" t="b">
         <v>0</v>
       </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
       <c r="AJ48" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6349,35 +6137,30 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>granlåga knäckt</t>
-        </is>
-      </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga knäckt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126034871</v>
+        <v>125598057</v>
       </c>
       <c r="B49" t="n">
-        <v>91210</v>
+        <v>57950</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6385,37 +6168,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mossamyran, Vb</t>
+          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>768896</v>
+        <v>770047</v>
       </c>
       <c r="R49" t="n">
-        <v>7087072</v>
+        <v>7086919</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6439,12 +6227,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6466,39 +6264,34 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL49" t="inlineStr">
-        <is>
-          <t>Granlåga, knäckt,  tunnare nedsänkt mossa</t>
-        </is>
-      </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt,  tunnare nedsänkt mossa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126034890</v>
+        <v>125598713</v>
       </c>
       <c r="B50" t="n">
-        <v>57654</v>
+        <v>57950</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -6527,17 +6320,17 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mossamyran, Vb</t>
+          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>768927</v>
+        <v>770013</v>
       </c>
       <c r="R50" t="n">
-        <v>7087074</v>
+        <v>7086998</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6561,12 +6354,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6578,6 +6381,11 @@
       <c r="AG50" t="b">
         <v>0</v>
       </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
       <c r="AJ50" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6588,52 +6396,47 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>Död, stående</t>
-        </is>
-      </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Picea abies # Död, stående</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126034880</v>
+        <v>125598946</v>
       </c>
       <c r="B51" t="n">
-        <v>57657</v>
+        <v>57950</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6649,17 +6452,17 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mossamyran, Vb</t>
+          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>769558</v>
+        <v>769979</v>
       </c>
       <c r="R51" t="n">
-        <v>7087012</v>
+        <v>7087051</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6683,17 +6486,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack äldre, lågt ned på stammen</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6704,6 +6512,11 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -6723,60 +6536,65 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126034877</v>
+        <v>125599155</v>
       </c>
       <c r="B52" t="n">
-        <v>91245</v>
+        <v>57950</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mossamyran, Vb</t>
+          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>769560</v>
+        <v>769958</v>
       </c>
       <c r="R52" t="n">
-        <v>7087013</v>
+        <v>7087078</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6800,12 +6618,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6817,6 +6645,11 @@
       <c r="AG52" t="b">
         <v>0</v>
       </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
       <c r="AJ52" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6827,35 +6660,30 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL52" t="inlineStr">
-        <is>
-          <t>Granlåga, knäckt</t>
-        </is>
-      </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126034872</v>
+        <v>125957531</v>
       </c>
       <c r="B53" t="n">
-        <v>91210</v>
+        <v>57950</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6863,37 +6691,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mossamyran, Vb</t>
+          <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>769400</v>
+        <v>769372</v>
       </c>
       <c r="R53" t="n">
-        <v>7086922</v>
+        <v>7087093</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6920,11 +6753,21 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6934,6 +6777,11 @@
       <c r="AG53" t="b">
         <v>0</v>
       </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
       <c r="AJ53" t="inlineStr">
         <is>
           <t>gran</t>
@@ -6944,35 +6792,30 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL53" t="inlineStr">
-        <is>
-          <t>Granlåga, knäckt</t>
-        </is>
-      </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga, knäckt</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126034869</v>
+        <v>126034887</v>
       </c>
       <c r="B54" t="n">
-        <v>91210</v>
+        <v>57950</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6980,34 +6823,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>769400</v>
+        <v>768983</v>
       </c>
       <c r="R54" t="n">
-        <v>7087029</v>
+        <v>7087100</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7063,12 +6911,12 @@
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>granlåga rotvälta</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Picea abies # granlåga rotvälta</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7086,14 +6934,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126034894</v>
+        <v>126034888</v>
       </c>
       <c r="B55" t="n">
-        <v>57654</v>
+        <v>57950</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -7126,10 +6974,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>768858</v>
+        <v>768983</v>
       </c>
       <c r="R55" t="n">
-        <v>7087093</v>
+        <v>7087104</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7185,12 +7033,12 @@
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>Död, knäckt</t>
+          <t>Levande</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Picea abies # Död, knäckt</t>
+          <t>Picea abies # Levande</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7208,45 +7056,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126034900</v>
+        <v>126034889</v>
       </c>
       <c r="B56" t="n">
-        <v>91241</v>
+        <v>57950</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>768994</v>
+        <v>768845</v>
       </c>
       <c r="R56" t="n">
-        <v>7086995</v>
+        <v>7087079</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7281,6 +7134,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Aktiva trämyror</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7302,12 +7160,12 @@
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>Gran stående</t>
+          <t>Död, stående</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Picea abies # Gran stående</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7325,14 +7183,14 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126034891</v>
+        <v>126034890</v>
       </c>
       <c r="B57" t="n">
-        <v>57654</v>
+        <v>57950</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -7365,10 +7223,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>768972</v>
+        <v>768927</v>
       </c>
       <c r="R57" t="n">
-        <v>7087057</v>
+        <v>7087074</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7447,14 +7305,14 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126034896</v>
+        <v>126034891</v>
       </c>
       <c r="B58" t="n">
-        <v>57654</v>
+        <v>57950</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -7478,7 +7336,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7487,10 +7345,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>769081</v>
+        <v>768972</v>
       </c>
       <c r="R58" t="n">
-        <v>7087072</v>
+        <v>7087057</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7525,11 +7383,6 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Basen av granen</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7549,9 +7402,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>Död, stående</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7569,14 +7427,14 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126034887</v>
+        <v>126034892</v>
       </c>
       <c r="B59" t="n">
-        <v>57654</v>
+        <v>57950</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -7609,10 +7467,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>768983</v>
+        <v>768979</v>
       </c>
       <c r="R59" t="n">
-        <v>7087100</v>
+        <v>7087095</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7668,12 +7526,12 @@
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>Levande</t>
+          <t>Död, stående</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7691,45 +7549,50 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126034903</v>
+        <v>126034893</v>
       </c>
       <c r="B60" t="n">
-        <v>78980</v>
+        <v>57950</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>768982</v>
+        <v>768983</v>
       </c>
       <c r="R60" t="n">
-        <v>7087094</v>
+        <v>7087095</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7785,12 +7648,12 @@
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>Död gran</t>
+          <t>Död, stående</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies # Död gran</t>
+          <t>Picea abies # Död, stående</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7808,10 +7671,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126034870</v>
+        <v>126034894</v>
       </c>
       <c r="B61" t="n">
-        <v>91210</v>
+        <v>57950</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7819,34 +7682,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>769323</v>
+        <v>768858</v>
       </c>
       <c r="R61" t="n">
-        <v>7087087</v>
+        <v>7087093</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7902,12 +7770,12 @@
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>Granlåga över bäck</t>
+          <t>Död, knäckt</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga över bäck</t>
+          <t>Picea abies # Död, knäckt</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7925,14 +7793,14 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126034888</v>
+        <v>126034896</v>
       </c>
       <c r="B62" t="n">
-        <v>57654</v>
+        <v>57950</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -7956,7 +7824,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7965,10 +7833,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>768983</v>
+        <v>769081</v>
       </c>
       <c r="R62" t="n">
-        <v>7087104</v>
+        <v>7087072</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8003,6 +7871,11 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Basen av granen</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -8022,14 +7895,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL62" t="inlineStr">
-        <is>
-          <t>Levande</t>
-        </is>
-      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Picea abies # Levande</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8047,32 +7915,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126034876</v>
+        <v>126077590</v>
       </c>
       <c r="B63" t="n">
-        <v>91245</v>
+        <v>57950</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8082,13 +7950,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>769088</v>
+        <v>769228</v>
       </c>
       <c r="R63" t="n">
-        <v>7087046</v>
+        <v>7086980</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8112,12 +7980,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8128,46 +7996,26 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL63" t="inlineStr">
-        <is>
-          <t>Granlåga, knäckt, delvis nedsjunken i mossa</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga, knäckt, delvis nedsjunken i mossa</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126034873</v>
+        <v>126077591</v>
       </c>
       <c r="B64" t="n">
-        <v>91210</v>
+        <v>57950</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8175,21 +8023,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8199,13 +8047,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>768910</v>
+        <v>769239</v>
       </c>
       <c r="R64" t="n">
-        <v>7087060</v>
+        <v>7086965</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8229,12 +8077,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8245,46 +8093,26 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL64" t="inlineStr">
-        <is>
-          <t>Granlåga, knäckt</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga, knäckt</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126077588</v>
+        <v>126077592</v>
       </c>
       <c r="B65" t="n">
-        <v>98382</v>
+        <v>57950</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8292,21 +8120,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8316,10 +8144,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>769260</v>
+        <v>769236</v>
       </c>
       <c r="R65" t="n">
-        <v>7087017</v>
+        <v>7086947</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8378,45 +8206,53 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126077586</v>
+        <v>126077593</v>
       </c>
       <c r="B66" t="n">
-        <v>91245</v>
+        <v>57899</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>100067</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>769682</v>
+        <v>769409</v>
       </c>
       <c r="R66" t="n">
-        <v>7087017</v>
+        <v>7086942</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8475,10 +8311,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126077591</v>
+        <v>125597783</v>
       </c>
       <c r="B67" t="n">
-        <v>57654</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8486,16 +8322,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8503,20 +8339,44 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Mossamyran, Vb</t>
+          <t>Sandån, Täftefjärden, Täfteå, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>769239</v>
+        <v>770048</v>
       </c>
       <c r="R67" t="n">
-        <v>7086965</v>
+        <v>7086917</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8540,12 +8400,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8556,26 +8426,46 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126077598</v>
+        <v>126034878</v>
       </c>
       <c r="B68" t="n">
-        <v>91263</v>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8583,37 +8473,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>769701</v>
+        <v>769399</v>
       </c>
       <c r="R68" t="n">
-        <v>7086999</v>
+        <v>7086925</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8637,12 +8532,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8651,67 +8551,71 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126077587</v>
+        <v>126034880</v>
       </c>
       <c r="B69" t="n">
-        <v>98382</v>
+        <v>57953</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>769274</v>
+        <v>769558</v>
       </c>
       <c r="R69" t="n">
-        <v>7087024</v>
+        <v>7087012</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8735,12 +8639,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack äldre, lågt ned på stammen</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8751,26 +8660,41 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126077593</v>
+        <v>126034881</v>
       </c>
       <c r="B70" t="n">
-        <v>57603</v>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8778,16 +8702,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100067</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8796,27 +8720,24 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>769409</v>
+        <v>768925</v>
       </c>
       <c r="R70" t="n">
-        <v>7086942</v>
+        <v>7087013</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8840,12 +8761,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8856,26 +8777,46 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL70" t="inlineStr">
+        <is>
+          <t>Granhögstubbe, knäckt</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies # Granhögstubbe, knäckt</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126077589</v>
+        <v>95744069</v>
       </c>
       <c r="B71" t="n">
-        <v>98382</v>
+        <v>5179</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8883,34 +8824,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mossamyran, Vb</t>
+          <t>S om Mossaberget, Vb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>769261</v>
+        <v>768831</v>
       </c>
       <c r="R71" t="n">
-        <v>7086996</v>
+        <v>7086985</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8937,12 +8883,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2021-08-24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2021-08-24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8953,43 +8899,48 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>däd gran</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126077590</v>
+        <v>126034899</v>
       </c>
       <c r="B72" t="n">
-        <v>57654</v>
+        <v>57132</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8997,20 +8948,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>avledningsbeteende</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>769228</v>
+        <v>769063</v>
       </c>
       <c r="R72" t="n">
-        <v>7086980</v>
+        <v>7087058</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9034,12 +8994,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9054,39 +9014,39 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126077592</v>
+        <v>125958446</v>
       </c>
       <c r="B73" t="n">
-        <v>57654</v>
+        <v>58327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -9094,17 +9054,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Mossamyran, Vb</t>
+          <t>Mossamyran, Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>769236</v>
+        <v>769311</v>
       </c>
       <c r="R73" t="n">
-        <v>7086947</v>
+        <v>7087040</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9131,12 +9105,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9147,26 +9131,46 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Blåbärsblandskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Katharina Radloff</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126077585</v>
+        <v>126077597</v>
       </c>
       <c r="B74" t="n">
-        <v>91210</v>
+        <v>58636</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9174,34 +9178,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>103044</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>769715</v>
+        <v>769245</v>
       </c>
       <c r="R74" t="n">
-        <v>7087020</v>
+        <v>7087082</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9260,10 +9272,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126077597</v>
+        <v>111316855</v>
       </c>
       <c r="B75" t="n">
-        <v>58334</v>
+        <v>5199</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9271,16 +9283,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103044</v>
+        <v>105930</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -9289,24 +9301,21 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Mossamyran, Vb</t>
+          <t>Mossaberget SV Täfteå, Vb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>769245</v>
+        <v>768836</v>
       </c>
       <c r="R75" t="n">
-        <v>7087082</v>
+        <v>7086987</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9333,12 +9342,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9349,26 +9358,31 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>död gran</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Andreas Garpebring, Åsa Gustafsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126073254</v>
+        <v>126073253</v>
       </c>
       <c r="B76" t="n">
-        <v>98382</v>
+        <v>99140</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9400,10 +9414,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>769266</v>
+        <v>769289</v>
       </c>
       <c r="R76" t="n">
-        <v>7087014</v>
+        <v>7087027</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9462,10 +9476,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126073253</v>
+        <v>126073254</v>
       </c>
       <c r="B77" t="n">
-        <v>98382</v>
+        <v>99140</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9497,10 +9511,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>769289</v>
+        <v>769266</v>
       </c>
       <c r="R77" t="n">
-        <v>7087027</v>
+        <v>7087014</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9559,57 +9573,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126131470</v>
+        <v>126077587</v>
       </c>
       <c r="B78" t="n">
-        <v>91259</v>
+        <v>99140</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1204</v>
+        <v>221952</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Mossamyran, Mossamyran, Vb</t>
+          <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>769374</v>
+        <v>769274</v>
       </c>
       <c r="R78" t="n">
-        <v>7086933</v>
+        <v>7087024</v>
       </c>
       <c r="S78" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9633,22 +9638,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:07</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:07</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9659,46 +9654,26 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Katharina Radloff</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126073252</v>
+        <v>126077588</v>
       </c>
       <c r="B79" t="n">
-        <v>80112</v>
+        <v>99140</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9706,34 +9681,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ultervik, Vb</t>
+          <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>769723</v>
+        <v>769260</v>
       </c>
       <c r="R79" t="n">
-        <v>7086893</v>
+        <v>7087017</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9780,22 +9755,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126073251</v>
+        <v>126077589</v>
       </c>
       <c r="B80" t="n">
-        <v>80112</v>
+        <v>99140</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9803,37 +9778,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Ultervik, Vb</t>
+          <t>Mossamyran, Vb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>769759</v>
+        <v>769261</v>
       </c>
       <c r="R80" t="n">
-        <v>7086899</v>
+        <v>7086996</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9874,82 +9846,63 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126073268</v>
+        <v>111740936</v>
       </c>
       <c r="B81" t="n">
-        <v>80118</v>
+        <v>92329</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6463</v>
+        <v>6040186</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Ultervik, Vb</t>
+          <t>Sandån-Täftefjärden, Vb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>769724</v>
+        <v>769779</v>
       </c>
       <c r="R81" t="n">
-        <v>7086894</v>
+        <v>7087057</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9976,12 +9929,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9990,385 +9943,21 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Maria Wikdahl</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>126073262</v>
-      </c>
-      <c r="B82" t="n">
-        <v>78980</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Ultervik, Vb</t>
-        </is>
-      </c>
-      <c r="Q82" t="n">
-        <v>769557</v>
-      </c>
-      <c r="R82" t="n">
-        <v>7086952</v>
-      </c>
-      <c r="S82" t="n">
-        <v>10</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Sävar</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AD82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT82" t="inlineStr"/>
-      <c r="AW82" t="inlineStr">
-        <is>
-          <t>Maria Wikdahl</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>Maria Wikdahl</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>126073257</v>
-      </c>
-      <c r="B83" t="n">
-        <v>80083</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Ultervik, Vb</t>
-        </is>
-      </c>
-      <c r="Q83" t="n">
-        <v>769727</v>
-      </c>
-      <c r="R83" t="n">
-        <v>7086890</v>
-      </c>
-      <c r="S83" t="n">
-        <v>10</v>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>Sävar</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>2025-06-19</t>
-        </is>
-      </c>
-      <c r="AD83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF83" t="inlineStr"/>
-      <c r="AG83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AT83" t="inlineStr"/>
-      <c r="AW83" t="inlineStr">
-        <is>
-          <t>Maria Wikdahl</t>
-        </is>
-      </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>Maria Wikdahl</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>125593294</v>
-      </c>
-      <c r="B84" t="n">
-        <v>57972</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Mossamyran, Mossamyran, Vb</t>
-        </is>
-      </c>
-      <c r="Q84" t="n">
-        <v>769751</v>
-      </c>
-      <c r="R84" t="n">
-        <v>7086871</v>
-      </c>
-      <c r="S84" t="n">
-        <v>2</v>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>Sävar</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>10:09</t>
-        </is>
-      </c>
-      <c r="AD84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE84" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AT84" t="inlineStr"/>
-      <c r="AW84" t="inlineStr">
-        <is>
-          <t>Katharina Radloff</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>Katharina Radloff</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24934-2025 artfynd.xlsx
+++ b/artfynd/A 24934-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY81"/>
+  <dimension ref="A1:AZ81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034898</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -930,6 +940,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125956621</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034900</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,6 +1164,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111740892</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,6 +1286,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034875</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1378,6 +1408,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034876</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1495,6 +1530,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034877</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1592,6 +1632,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126077586</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1728,6 +1773,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126131470</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1831,6 +1881,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111316850</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1928,6 +1983,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111740881</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2025,6 +2085,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111740882</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2122,6 +2187,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111740883</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2249,6 +2319,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125957105</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2366,6 +2441,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034867</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2483,6 +2563,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034869</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2600,6 +2685,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034870</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2717,6 +2807,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034871</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2834,6 +2929,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034872</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2951,6 +3051,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034873</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3068,6 +3173,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034874</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3165,6 +3275,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126077585</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3262,6 +3377,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95744068</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3364,6 +3484,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111316854</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3461,6 +3586,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111740961</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3597,6 +3727,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125592263</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3733,6 +3868,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125592468</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3872,6 +4012,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125596546</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4008,6 +4153,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125599815</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4144,6 +4294,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125601124</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4275,6 +4430,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125955277</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4411,6 +4571,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125956746</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4547,6 +4712,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125957354</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4683,6 +4853,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125957578</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4800,6 +4975,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034903</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4897,6 +5077,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126073262</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4994,6 +5179,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111740938</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5111,6 +5301,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034897</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5227,6 +5422,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126073257</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5343,6 +5543,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126073251</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5440,6 +5645,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126073252</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5556,6 +5766,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126073268</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5658,6 +5873,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111740915</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5755,6 +5975,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111740916</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5890,6 +6115,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125593294</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6022,6 +6252,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125595152</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6154,6 +6389,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125595361</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6281,6 +6521,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598057</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6413,6 +6658,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598713</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6545,6 +6795,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125598946</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6677,6 +6932,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125599155</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6809,6 +7069,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125957531</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6931,6 +7196,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034887</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7053,6 +7323,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034888</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7180,6 +7455,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034889</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7302,6 +7582,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034890</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7424,6 +7709,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034891</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7546,6 +7836,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034892</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7668,6 +7963,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034893</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7790,6 +8090,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034894</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7912,6 +8217,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034896</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8009,6 +8319,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126077590</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8106,6 +8421,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126077591</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8203,6 +8523,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126077592</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8308,6 +8633,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126077593</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8459,6 +8789,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125597783</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8566,6 +8901,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034878</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8688,6 +9028,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034880</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8810,6 +9155,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034881</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8917,6 +9267,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95744069</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9023,6 +9378,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034899</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9164,6 +9524,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125958446</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9269,6 +9634,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126077597</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9376,6 +9746,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111316855</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9473,6 +9848,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126073253</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9570,6 +9950,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126073254</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9667,6 +10052,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126077587</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9764,6 +10154,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126077588</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9861,6 +10256,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126077589</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9958,8 +10358,95 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111740936</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>